--- a/zadanie1/Solution checker2.xlsx
+++ b/zadanie1/Solution checker2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kamie\Projekty\Inteligentne metody opymalizacji\zadanie1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8582ACE8-7420-4A7D-8228-424E5FA547D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92832B5D-4453-4BE0-92FF-98912E006D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14303" yWindow="-2190" windowWidth="19394" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TSPA" sheetId="4" r:id="rId1"/>
@@ -486,15 +486,15 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1">
         <f>SUM(I3:I202)</f>
-        <v>31413</v>
+        <v>29323</v>
       </c>
       <c r="J2" s="1">
         <f>SUM(J3:J202)</f>
-        <v>27045</v>
+        <v>21542</v>
       </c>
       <c r="K2" s="4">
         <f>I2-J2</f>
-        <v>4368</v>
+        <v>7781</v>
       </c>
       <c r="L2" s="1"/>
       <c r="O2" t="str">
@@ -518,39 +518,39 @@
         <v>233</v>
       </c>
       <c r="F3" s="2">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="G3">
         <f>IF(NOT(R3),M3,"")</f>
-        <v>3796</v>
+        <v>2065</v>
       </c>
       <c r="H3">
         <f>IF(NOT(R3),N3,"")</f>
-        <v>244</v>
+        <v>430</v>
       </c>
       <c r="I3">
         <f>IF(NOT(R3),O3,"")</f>
-        <v>324</v>
+        <v>213</v>
       </c>
       <c r="J3">
         <f>IF(S3,Q3,IF(NOT(R3),P3,""))</f>
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="M3">
         <f>LOOKUP($F3,$A$3:$A$202,B$3:B$202)</f>
-        <v>3796</v>
+        <v>2065</v>
       </c>
       <c r="N3">
         <f>LOOKUP($F3,$A$3:$A$202,C$3:C$202)</f>
-        <v>244</v>
+        <v>430</v>
       </c>
       <c r="O3">
         <f>LOOKUP($F3,$A$3:$A$202,D$3:D$202)</f>
-        <v>324</v>
+        <v>213</v>
       </c>
       <c r="P3">
         <f>INT(SQRT((M3-M4)*(M3-M4)+(N3-N4)*(N3-N4)) +0.5)</f>
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="Q3">
         <f>INT(SQRT((M$3-M3)*(M$3-M3)+(N$3-N3)*(N$3-N3)) +0.5)</f>
@@ -579,43 +579,43 @@
         <v>241</v>
       </c>
       <c r="F4" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G4">
         <f t="shared" ref="G4:G67" si="1">IF(NOT(R4),M4,"")</f>
-        <v>3848</v>
+        <v>2088</v>
       </c>
       <c r="H4">
         <f t="shared" ref="H4:H67" si="2">IF(NOT(R4),N4,"")</f>
-        <v>355</v>
+        <v>453</v>
       </c>
       <c r="I4">
         <f t="shared" ref="I4:I67" si="3">IF(NOT(R4),O4,"")</f>
-        <v>173</v>
+        <v>32</v>
       </c>
       <c r="J4">
         <f t="shared" ref="J4:J67" si="4">IF(S4,Q4,IF(NOT(R4),P4,""))</f>
-        <v>195</v>
+        <v>132</v>
       </c>
       <c r="M4">
         <f t="shared" ref="M4:M35" si="5">LOOKUP($F4,$A$3:$A$202,B$3:B$202)</f>
-        <v>3848</v>
+        <v>2088</v>
       </c>
       <c r="N4">
         <f t="shared" ref="N4:N35" si="6">LOOKUP($F4,$A$3:$A$202,C$3:C$202)</f>
-        <v>355</v>
+        <v>453</v>
       </c>
       <c r="O4">
         <f t="shared" ref="O4:O67" si="7">LOOKUP($F4,$A$3:$A$202,D$3:D$202)</f>
-        <v>173</v>
+        <v>32</v>
       </c>
       <c r="P4">
         <f t="shared" ref="P4:P67" si="8">INT(SQRT((M4-M5)*(M4-M5)+(N4-N5)*(N4-N5)) +0.5)</f>
-        <v>195</v>
+        <v>132</v>
       </c>
       <c r="Q4">
         <f t="shared" ref="Q4:Q67" si="9">INT(SQRT((M$3-M4)*(M$3-M4)+(N$3-N4)*(N$3-N4)) +0.5)</f>
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="R4" t="b">
         <f t="shared" si="0"/>
@@ -640,43 +640,43 @@
         <v>66</v>
       </c>
       <c r="F5" s="2">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="G5">
         <f t="shared" si="1"/>
-        <v>3735</v>
+        <v>2218</v>
       </c>
       <c r="H5">
         <f t="shared" si="2"/>
-        <v>514</v>
+        <v>431</v>
       </c>
       <c r="I5">
         <f t="shared" si="3"/>
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J5">
         <f t="shared" si="4"/>
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="M5">
         <f t="shared" si="5"/>
-        <v>3735</v>
+        <v>2218</v>
       </c>
       <c r="N5">
         <f t="shared" si="6"/>
-        <v>514</v>
+        <v>431</v>
       </c>
       <c r="O5">
         <f t="shared" si="7"/>
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P5">
         <f t="shared" si="8"/>
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="Q5">
         <f t="shared" si="9"/>
-        <v>277</v>
+        <v>153</v>
       </c>
       <c r="R5" t="b">
         <f t="shared" si="0"/>
@@ -701,43 +701,43 @@
         <v>80</v>
       </c>
       <c r="F6" s="2">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="G6">
         <f t="shared" si="1"/>
-        <v>3734</v>
+        <v>2246</v>
       </c>
       <c r="H6">
         <f t="shared" si="2"/>
-        <v>657</v>
+        <v>490</v>
       </c>
       <c r="I6">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>261</v>
       </c>
       <c r="J6">
         <f t="shared" si="4"/>
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="M6">
         <f t="shared" si="5"/>
-        <v>3734</v>
+        <v>2246</v>
       </c>
       <c r="N6">
         <f t="shared" si="6"/>
-        <v>657</v>
+        <v>490</v>
       </c>
       <c r="O6">
         <f t="shared" si="7"/>
-        <v>34</v>
+        <v>261</v>
       </c>
       <c r="P6">
         <f t="shared" si="8"/>
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="Q6">
         <f t="shared" si="9"/>
-        <v>418</v>
+        <v>191</v>
       </c>
       <c r="R6" t="b">
         <f t="shared" si="0"/>
@@ -762,43 +762,43 @@
         <v>264</v>
       </c>
       <c r="F7" s="2">
-        <v>196</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <f t="shared" si="1"/>
-        <v>3688</v>
+        <v>2343</v>
       </c>
       <c r="H7">
         <f t="shared" si="2"/>
-        <v>759</v>
+        <v>360</v>
       </c>
       <c r="I7">
         <f t="shared" si="3"/>
-        <v>346</v>
+        <v>159</v>
       </c>
       <c r="J7">
         <f t="shared" si="4"/>
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="M7">
         <f t="shared" si="5"/>
-        <v>3688</v>
+        <v>2343</v>
       </c>
       <c r="N7">
         <f t="shared" si="6"/>
-        <v>759</v>
+        <v>360</v>
       </c>
       <c r="O7">
         <f t="shared" si="7"/>
-        <v>346</v>
+        <v>159</v>
       </c>
       <c r="P7">
         <f t="shared" si="8"/>
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="Q7">
         <f t="shared" si="9"/>
-        <v>526</v>
+        <v>287</v>
       </c>
       <c r="R7" t="b">
         <f t="shared" si="0"/>
@@ -823,43 +823,43 @@
         <v>87</v>
       </c>
       <c r="F8" s="2">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>3901</v>
+        <v>2371</v>
       </c>
       <c r="H8">
         <f t="shared" si="2"/>
-        <v>849</v>
+        <v>371</v>
       </c>
       <c r="I8">
         <f t="shared" si="3"/>
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="J8">
         <f t="shared" si="4"/>
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="M8">
         <f t="shared" si="5"/>
-        <v>3901</v>
+        <v>2371</v>
       </c>
       <c r="N8">
         <f t="shared" si="6"/>
-        <v>849</v>
+        <v>371</v>
       </c>
       <c r="O8">
         <f t="shared" si="7"/>
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="P8">
         <f t="shared" si="8"/>
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="Q8">
         <f t="shared" si="9"/>
-        <v>614</v>
+        <v>312</v>
       </c>
       <c r="R8" t="b">
         <f t="shared" si="0"/>
@@ -884,43 +884,43 @@
         <v>311</v>
       </c>
       <c r="F9" s="2">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>3903</v>
+        <v>2465</v>
       </c>
       <c r="H9">
         <f t="shared" si="2"/>
-        <v>911</v>
+        <v>426</v>
       </c>
       <c r="I9">
         <f t="shared" si="3"/>
-        <v>223</v>
+        <v>98</v>
       </c>
       <c r="J9">
         <f t="shared" si="4"/>
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M9">
         <f t="shared" si="5"/>
-        <v>3903</v>
+        <v>2465</v>
       </c>
       <c r="N9">
         <f t="shared" si="6"/>
-        <v>911</v>
+        <v>426</v>
       </c>
       <c r="O9">
         <f t="shared" si="7"/>
-        <v>223</v>
+        <v>98</v>
       </c>
       <c r="P9">
         <f t="shared" si="8"/>
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q9">
         <f t="shared" si="9"/>
-        <v>676</v>
+        <v>400</v>
       </c>
       <c r="R9" t="b">
         <f t="shared" si="0"/>
@@ -945,43 +945,43 @@
         <v>305</v>
       </c>
       <c r="F10" s="2">
-        <v>174</v>
+        <v>101</v>
       </c>
       <c r="G10">
         <f t="shared" si="1"/>
-        <v>3797</v>
+        <v>2504</v>
       </c>
       <c r="H10">
         <f t="shared" si="2"/>
-        <v>990</v>
+        <v>302</v>
       </c>
       <c r="I10">
         <f t="shared" si="3"/>
-        <v>244</v>
+        <v>325</v>
       </c>
       <c r="J10">
         <f t="shared" si="4"/>
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="M10">
         <f t="shared" si="5"/>
-        <v>3797</v>
+        <v>2504</v>
       </c>
       <c r="N10">
         <f t="shared" si="6"/>
-        <v>990</v>
+        <v>302</v>
       </c>
       <c r="O10">
         <f t="shared" si="7"/>
-        <v>244</v>
+        <v>325</v>
       </c>
       <c r="P10">
         <f t="shared" si="8"/>
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="Q10">
         <f t="shared" si="9"/>
-        <v>746</v>
+        <v>457</v>
       </c>
       <c r="R10" t="b">
         <f t="shared" si="0"/>
@@ -1006,43 +1006,43 @@
         <v>281</v>
       </c>
       <c r="F11" s="2">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="G11">
         <f t="shared" si="1"/>
-        <v>3661</v>
+        <v>2540</v>
       </c>
       <c r="H11">
         <f t="shared" si="2"/>
-        <v>867</v>
+        <v>260</v>
       </c>
       <c r="I11">
         <f t="shared" si="3"/>
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="J11">
         <f t="shared" si="4"/>
-        <v>261</v>
+        <v>128</v>
       </c>
       <c r="M11">
         <f t="shared" si="5"/>
-        <v>3661</v>
+        <v>2540</v>
       </c>
       <c r="N11">
         <f t="shared" si="6"/>
-        <v>867</v>
+        <v>260</v>
       </c>
       <c r="O11">
         <f t="shared" si="7"/>
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="P11">
         <f t="shared" si="8"/>
-        <v>261</v>
+        <v>128</v>
       </c>
       <c r="Q11">
         <f t="shared" si="9"/>
-        <v>637</v>
+        <v>505</v>
       </c>
       <c r="R11" t="b">
         <f t="shared" si="0"/>
@@ -1067,43 +1067,43 @@
         <v>306</v>
       </c>
       <c r="F12" s="2">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>3430</v>
+        <v>2524</v>
       </c>
       <c r="H12">
         <f t="shared" si="2"/>
-        <v>746</v>
+        <v>387</v>
       </c>
       <c r="I12">
         <f t="shared" si="3"/>
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="J12">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="M12">
         <f t="shared" si="5"/>
-        <v>3430</v>
+        <v>2524</v>
       </c>
       <c r="N12">
         <f t="shared" si="6"/>
-        <v>746</v>
+        <v>387</v>
       </c>
       <c r="O12">
         <f t="shared" si="7"/>
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="P12">
         <f t="shared" si="8"/>
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="Q12">
         <f t="shared" si="9"/>
-        <v>621</v>
+        <v>461</v>
       </c>
       <c r="R12" t="b">
         <f t="shared" si="0"/>
@@ -1128,43 +1128,43 @@
         <v>235</v>
       </c>
       <c r="F13" s="2">
-        <v>179</v>
+        <v>87</v>
       </c>
       <c r="G13">
         <f t="shared" si="1"/>
-        <v>3369</v>
+        <v>2685</v>
       </c>
       <c r="H13">
         <f t="shared" si="2"/>
-        <v>697</v>
+        <v>520</v>
       </c>
       <c r="I13">
         <f t="shared" si="3"/>
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="J13">
         <f t="shared" si="4"/>
-        <v>396</v>
+        <v>88</v>
       </c>
       <c r="M13">
         <f t="shared" si="5"/>
-        <v>3369</v>
+        <v>2685</v>
       </c>
       <c r="N13">
         <f t="shared" si="6"/>
-        <v>697</v>
+        <v>520</v>
       </c>
       <c r="O13">
         <f t="shared" si="7"/>
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="P13">
         <f t="shared" si="8"/>
-        <v>396</v>
+        <v>88</v>
       </c>
       <c r="Q13">
         <f t="shared" si="9"/>
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="R13" t="b">
         <f t="shared" si="0"/>
@@ -1189,43 +1189,43 @@
         <v>281</v>
       </c>
       <c r="F14" s="2">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="G14">
         <f t="shared" si="1"/>
-        <v>3469</v>
+        <v>2605</v>
       </c>
       <c r="H14">
         <f t="shared" si="2"/>
-        <v>1080</v>
+        <v>556</v>
       </c>
       <c r="I14">
         <f t="shared" si="3"/>
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="J14">
         <f t="shared" si="4"/>
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M14">
         <f t="shared" si="5"/>
-        <v>3469</v>
+        <v>2605</v>
       </c>
       <c r="N14">
         <f t="shared" si="6"/>
-        <v>1080</v>
+        <v>556</v>
       </c>
       <c r="O14">
         <f t="shared" si="7"/>
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="P14">
         <f t="shared" si="8"/>
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="Q14">
         <f t="shared" si="9"/>
-        <v>898</v>
+        <v>555</v>
       </c>
       <c r="R14" t="b">
         <f t="shared" si="0"/>
@@ -1250,43 +1250,43 @@
         <v>188</v>
       </c>
       <c r="F15" s="2">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G15">
         <f t="shared" si="1"/>
-        <v>3585</v>
+        <v>2571</v>
       </c>
       <c r="H15">
         <f t="shared" si="2"/>
-        <v>1109</v>
+        <v>560</v>
       </c>
       <c r="I15">
         <f t="shared" si="3"/>
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="J15">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M15">
         <f t="shared" si="5"/>
-        <v>3585</v>
+        <v>2571</v>
       </c>
       <c r="N15">
         <f t="shared" si="6"/>
-        <v>1109</v>
+        <v>560</v>
       </c>
       <c r="O15">
         <f t="shared" si="7"/>
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="P15">
         <f t="shared" si="8"/>
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Q15">
         <f t="shared" si="9"/>
-        <v>890</v>
+        <v>522</v>
       </c>
       <c r="R15" t="b">
         <f t="shared" si="0"/>
@@ -1311,43 +1311,43 @@
         <v>94</v>
       </c>
       <c r="F16" s="2">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="G16">
         <f t="shared" si="1"/>
-        <v>3587</v>
+        <v>2549</v>
       </c>
       <c r="H16">
         <f t="shared" si="2"/>
-        <v>1123</v>
+        <v>554</v>
       </c>
       <c r="I16">
         <f t="shared" si="3"/>
-        <v>219</v>
+        <v>99</v>
       </c>
       <c r="J16">
         <f t="shared" si="4"/>
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="M16">
         <f t="shared" si="5"/>
-        <v>3587</v>
+        <v>2549</v>
       </c>
       <c r="N16">
         <f t="shared" si="6"/>
-        <v>1123</v>
+        <v>554</v>
       </c>
       <c r="O16">
         <f t="shared" si="7"/>
-        <v>219</v>
+        <v>99</v>
       </c>
       <c r="P16">
         <f t="shared" si="8"/>
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="Q16">
         <f t="shared" si="9"/>
-        <v>904</v>
+        <v>500</v>
       </c>
       <c r="R16" t="b">
         <f t="shared" si="0"/>
@@ -1372,43 +1372,43 @@
         <v>61</v>
       </c>
       <c r="F17" s="2">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="G17">
         <f t="shared" si="1"/>
-        <v>3576</v>
+        <v>2346</v>
       </c>
       <c r="H17">
         <f t="shared" si="2"/>
-        <v>1287</v>
+        <v>573</v>
       </c>
       <c r="I17">
         <f t="shared" si="3"/>
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="J17">
         <f t="shared" si="4"/>
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="M17">
         <f t="shared" si="5"/>
-        <v>3576</v>
+        <v>2346</v>
       </c>
       <c r="N17">
         <f t="shared" si="6"/>
-        <v>1287</v>
+        <v>573</v>
       </c>
       <c r="O17">
         <f t="shared" si="7"/>
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="P17">
         <f t="shared" si="8"/>
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="Q17">
         <f t="shared" si="9"/>
-        <v>1066</v>
+        <v>315</v>
       </c>
       <c r="R17" t="b">
         <f t="shared" si="0"/>
@@ -1433,43 +1433,43 @@
         <v>170</v>
       </c>
       <c r="F18" s="2">
-        <v>39</v>
+        <v>189</v>
       </c>
       <c r="G18">
         <f t="shared" si="1"/>
-        <v>3637</v>
+        <v>2298</v>
       </c>
       <c r="H18">
         <f t="shared" si="2"/>
-        <v>1416</v>
+        <v>573</v>
       </c>
       <c r="I18">
         <f t="shared" si="3"/>
-        <v>231</v>
+        <v>85</v>
       </c>
       <c r="J18">
         <f t="shared" si="4"/>
-        <v>373</v>
+        <v>201</v>
       </c>
       <c r="M18">
         <f t="shared" si="5"/>
-        <v>3637</v>
+        <v>2298</v>
       </c>
       <c r="N18">
         <f t="shared" si="6"/>
-        <v>1416</v>
+        <v>573</v>
       </c>
       <c r="O18">
         <f t="shared" si="7"/>
-        <v>231</v>
+        <v>85</v>
       </c>
       <c r="P18">
         <f t="shared" si="8"/>
-        <v>373</v>
+        <v>201</v>
       </c>
       <c r="Q18">
         <f t="shared" si="9"/>
-        <v>1183</v>
+        <v>273</v>
       </c>
       <c r="R18" t="b">
         <f t="shared" si="0"/>
@@ -1494,43 +1494,43 @@
         <v>213</v>
       </c>
       <c r="F19" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G19">
         <f t="shared" si="1"/>
-        <v>3991</v>
+        <v>2237</v>
       </c>
       <c r="H19">
         <f t="shared" si="2"/>
-        <v>1300</v>
+        <v>764</v>
       </c>
       <c r="I19">
         <f t="shared" si="3"/>
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="J19">
         <f t="shared" si="4"/>
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="M19">
         <f t="shared" si="5"/>
-        <v>3991</v>
+        <v>2237</v>
       </c>
       <c r="N19">
         <f t="shared" si="6"/>
-        <v>1300</v>
+        <v>764</v>
       </c>
       <c r="O19">
         <f t="shared" si="7"/>
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="P19">
         <f t="shared" si="8"/>
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="Q19">
         <f t="shared" si="9"/>
-        <v>1074</v>
+        <v>376</v>
       </c>
       <c r="R19" t="b">
         <f t="shared" si="0"/>
@@ -1555,43 +1555,43 @@
         <v>34</v>
       </c>
       <c r="F20" s="2">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="G20">
         <f t="shared" si="1"/>
-        <v>3983</v>
+        <v>2207</v>
       </c>
       <c r="H20">
         <f t="shared" si="2"/>
-        <v>1428</v>
+        <v>907</v>
       </c>
       <c r="I20">
         <f t="shared" si="3"/>
-        <v>342</v>
+        <v>214</v>
       </c>
       <c r="J20">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="M20">
         <f t="shared" si="5"/>
-        <v>3983</v>
+        <v>2207</v>
       </c>
       <c r="N20">
         <f t="shared" si="6"/>
-        <v>1428</v>
+        <v>907</v>
       </c>
       <c r="O20">
         <f t="shared" si="7"/>
-        <v>342</v>
+        <v>214</v>
       </c>
       <c r="P20">
         <f t="shared" si="8"/>
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="Q20">
         <f t="shared" si="9"/>
-        <v>1199</v>
+        <v>498</v>
       </c>
       <c r="R20" t="b">
         <f t="shared" si="0"/>
@@ -1616,43 +1616,43 @@
         <v>153</v>
       </c>
       <c r="F21" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <f t="shared" si="1"/>
-        <v>3990</v>
+        <v>2219</v>
       </c>
       <c r="H21">
         <f t="shared" si="2"/>
-        <v>1450</v>
+        <v>964</v>
       </c>
       <c r="I21">
         <f t="shared" si="3"/>
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="J21">
         <f t="shared" si="4"/>
-        <v>229</v>
+        <v>164</v>
       </c>
       <c r="M21">
         <f t="shared" si="5"/>
-        <v>3990</v>
+        <v>2219</v>
       </c>
       <c r="N21">
         <f t="shared" si="6"/>
-        <v>1450</v>
+        <v>964</v>
       </c>
       <c r="O21">
         <f t="shared" si="7"/>
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="P21">
         <f t="shared" si="8"/>
-        <v>229</v>
+        <v>164</v>
       </c>
       <c r="Q21">
         <f t="shared" si="9"/>
-        <v>1222</v>
+        <v>556</v>
       </c>
       <c r="R21" t="b">
         <f t="shared" si="0"/>
@@ -1677,43 +1677,43 @@
         <v>305</v>
       </c>
       <c r="F22" s="2">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="G22">
         <f t="shared" si="1"/>
-        <v>3964</v>
+        <v>2337</v>
       </c>
       <c r="H22">
         <f t="shared" si="2"/>
-        <v>1678</v>
+        <v>850</v>
       </c>
       <c r="I22">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="J22">
         <f t="shared" si="4"/>
-        <v>170</v>
+        <v>255</v>
       </c>
       <c r="M22">
         <f t="shared" si="5"/>
-        <v>3964</v>
+        <v>2337</v>
       </c>
       <c r="N22">
         <f t="shared" si="6"/>
-        <v>1678</v>
+        <v>850</v>
       </c>
       <c r="O22">
         <f t="shared" si="7"/>
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="P22">
         <f t="shared" si="8"/>
-        <v>170</v>
+        <v>255</v>
       </c>
       <c r="Q22">
         <f t="shared" si="9"/>
-        <v>1444</v>
+        <v>500</v>
       </c>
       <c r="R22" t="b">
         <f t="shared" si="0"/>
@@ -1738,43 +1738,43 @@
         <v>125</v>
       </c>
       <c r="F23" s="2">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>3855</v>
+        <v>2559</v>
       </c>
       <c r="H23">
         <f t="shared" si="2"/>
-        <v>1808</v>
+        <v>975</v>
       </c>
       <c r="I23">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>228</v>
       </c>
       <c r="J23">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>237</v>
       </c>
       <c r="M23">
         <f t="shared" si="5"/>
-        <v>3855</v>
+        <v>2559</v>
       </c>
       <c r="N23">
         <f t="shared" si="6"/>
-        <v>1808</v>
+        <v>975</v>
       </c>
       <c r="O23">
         <f t="shared" si="7"/>
-        <v>37</v>
+        <v>228</v>
       </c>
       <c r="P23">
         <f t="shared" si="8"/>
-        <v>85</v>
+        <v>237</v>
       </c>
       <c r="Q23">
         <f t="shared" si="9"/>
-        <v>1565</v>
+        <v>736</v>
       </c>
       <c r="R23" t="b">
         <f t="shared" si="0"/>
@@ -1799,43 +1799,43 @@
         <v>186</v>
       </c>
       <c r="F24" s="2">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="G24">
         <f t="shared" si="1"/>
-        <v>3842</v>
+        <v>2498</v>
       </c>
       <c r="H24">
         <f t="shared" si="2"/>
-        <v>1892</v>
+        <v>1204</v>
       </c>
       <c r="I24">
         <f t="shared" si="3"/>
-        <v>325</v>
+        <v>107</v>
       </c>
       <c r="J24">
         <f t="shared" si="4"/>
-        <v>192</v>
+        <v>80</v>
       </c>
       <c r="M24">
         <f t="shared" si="5"/>
-        <v>3842</v>
+        <v>2498</v>
       </c>
       <c r="N24">
         <f t="shared" si="6"/>
-        <v>1892</v>
+        <v>1204</v>
       </c>
       <c r="O24">
         <f t="shared" si="7"/>
-        <v>325</v>
+        <v>107</v>
       </c>
       <c r="P24">
         <f t="shared" si="8"/>
-        <v>192</v>
+        <v>80</v>
       </c>
       <c r="Q24">
         <f t="shared" si="9"/>
-        <v>1649</v>
+        <v>887</v>
       </c>
       <c r="R24" t="b">
         <f t="shared" si="0"/>
@@ -1860,43 +1860,43 @@
         <v>160</v>
       </c>
       <c r="F25" s="2">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="G25">
         <f t="shared" si="1"/>
-        <v>3650</v>
+        <v>2573</v>
       </c>
       <c r="H25">
         <f t="shared" si="2"/>
-        <v>1882</v>
+        <v>1231</v>
       </c>
       <c r="I25">
         <f t="shared" si="3"/>
-        <v>305</v>
+        <v>34</v>
       </c>
       <c r="J25">
         <f t="shared" si="4"/>
-        <v>236</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <f t="shared" si="5"/>
-        <v>3650</v>
+        <v>2573</v>
       </c>
       <c r="N25">
         <f t="shared" si="6"/>
-        <v>1882</v>
+        <v>1231</v>
       </c>
       <c r="O25">
         <f t="shared" si="7"/>
-        <v>305</v>
+        <v>34</v>
       </c>
       <c r="P25">
         <f t="shared" si="8"/>
-        <v>236</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <f t="shared" si="9"/>
-        <v>1644</v>
+        <v>949</v>
       </c>
       <c r="R25" t="b">
         <f t="shared" si="0"/>
@@ -1921,43 +1921,43 @@
         <v>292</v>
       </c>
       <c r="F26" s="2">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="G26">
         <f t="shared" si="1"/>
-        <v>3691</v>
+        <v>2578</v>
       </c>
       <c r="H26">
         <f t="shared" si="2"/>
-        <v>1650</v>
+        <v>1230</v>
       </c>
       <c r="I26">
         <f t="shared" si="3"/>
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="J26">
         <f t="shared" si="4"/>
-        <v>473</v>
+        <v>267</v>
       </c>
       <c r="M26">
         <f t="shared" si="5"/>
-        <v>3691</v>
+        <v>2578</v>
       </c>
       <c r="N26">
         <f t="shared" si="6"/>
-        <v>1650</v>
+        <v>1230</v>
       </c>
       <c r="O26">
         <f t="shared" si="7"/>
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="P26">
         <f t="shared" si="8"/>
-        <v>473</v>
+        <v>267</v>
       </c>
       <c r="Q26">
         <f t="shared" si="9"/>
-        <v>1410</v>
+        <v>950</v>
       </c>
       <c r="R26" t="b">
         <f t="shared" si="0"/>
@@ -1982,43 +1982,43 @@
         <v>241</v>
       </c>
       <c r="F27" s="2">
-        <v>8</v>
+        <v>167</v>
       </c>
       <c r="G27">
         <f t="shared" si="1"/>
-        <v>3474</v>
+        <v>2682</v>
       </c>
       <c r="H27">
         <f t="shared" si="2"/>
-        <v>1230</v>
+        <v>984</v>
       </c>
       <c r="I27">
         <f t="shared" si="3"/>
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="J27">
         <f t="shared" si="4"/>
-        <v>300</v>
+        <v>239</v>
       </c>
       <c r="M27">
         <f t="shared" si="5"/>
-        <v>3474</v>
+        <v>2682</v>
       </c>
       <c r="N27">
         <f t="shared" si="6"/>
-        <v>1230</v>
+        <v>984</v>
       </c>
       <c r="O27">
         <f t="shared" si="7"/>
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="P27">
         <f t="shared" si="8"/>
-        <v>300</v>
+        <v>239</v>
       </c>
       <c r="Q27">
         <f t="shared" si="9"/>
-        <v>1037</v>
+        <v>829</v>
       </c>
       <c r="R27" t="b">
         <f t="shared" si="0"/>
@@ -2043,43 +2043,43 @@
         <v>50</v>
       </c>
       <c r="F28" s="2">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="G28">
         <f t="shared" si="1"/>
-        <v>3226</v>
+        <v>2861</v>
       </c>
       <c r="H28">
         <f t="shared" si="2"/>
-        <v>1399</v>
+        <v>825</v>
       </c>
       <c r="I28">
         <f t="shared" si="3"/>
-        <v>283</v>
+        <v>56</v>
       </c>
       <c r="J28">
         <f t="shared" si="4"/>
-        <v>161</v>
+        <v>313</v>
       </c>
       <c r="M28">
         <f t="shared" si="5"/>
-        <v>3226</v>
+        <v>2861</v>
       </c>
       <c r="N28">
         <f t="shared" si="6"/>
-        <v>1399</v>
+        <v>825</v>
       </c>
       <c r="O28">
         <f t="shared" si="7"/>
-        <v>283</v>
+        <v>56</v>
       </c>
       <c r="P28">
         <f t="shared" si="8"/>
-        <v>161</v>
+        <v>313</v>
       </c>
       <c r="Q28">
         <f t="shared" si="9"/>
-        <v>1288</v>
+        <v>889</v>
       </c>
       <c r="R28" t="b">
         <f t="shared" si="0"/>
@@ -2104,43 +2104,43 @@
         <v>156</v>
       </c>
       <c r="F29" s="2">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="G29">
         <f t="shared" si="1"/>
-        <v>3088</v>
+        <v>3023</v>
       </c>
       <c r="H29">
         <f t="shared" si="2"/>
-        <v>1482</v>
+        <v>557</v>
       </c>
       <c r="I29">
         <f t="shared" si="3"/>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J29">
         <f t="shared" si="4"/>
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="M29">
         <f t="shared" si="5"/>
-        <v>3088</v>
+        <v>3023</v>
       </c>
       <c r="N29">
         <f t="shared" si="6"/>
-        <v>1482</v>
+        <v>557</v>
       </c>
       <c r="O29">
         <f t="shared" si="7"/>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P29">
         <f t="shared" si="8"/>
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="Q29">
         <f t="shared" si="9"/>
-        <v>1426</v>
+        <v>966</v>
       </c>
       <c r="R29" t="b">
         <f t="shared" si="0"/>
@@ -2165,43 +2165,43 @@
         <v>172</v>
       </c>
       <c r="F30" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="G30">
         <f t="shared" si="1"/>
-        <v>2935</v>
+        <v>3069</v>
       </c>
       <c r="H30">
         <f t="shared" si="2"/>
-        <v>1553</v>
+        <v>412</v>
       </c>
       <c r="I30">
         <f t="shared" si="3"/>
-        <v>281</v>
+        <v>343</v>
       </c>
       <c r="J30">
         <f t="shared" si="4"/>
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="M30">
         <f t="shared" si="5"/>
-        <v>2935</v>
+        <v>3069</v>
       </c>
       <c r="N30">
         <f t="shared" si="6"/>
-        <v>1553</v>
+        <v>412</v>
       </c>
       <c r="O30">
         <f t="shared" si="7"/>
-        <v>281</v>
+        <v>343</v>
       </c>
       <c r="P30">
         <f t="shared" si="8"/>
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="Q30">
         <f t="shared" si="9"/>
-        <v>1567</v>
+        <v>1004</v>
       </c>
       <c r="R30" t="b">
         <f t="shared" si="0"/>
@@ -2226,43 +2226,43 @@
         <v>299</v>
       </c>
       <c r="F31" s="2">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="G31">
         <f t="shared" si="1"/>
-        <v>2898</v>
+        <v>3016</v>
       </c>
       <c r="H31">
         <f t="shared" si="2"/>
-        <v>1609</v>
+        <v>260</v>
       </c>
       <c r="I31">
         <f t="shared" si="3"/>
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="J31">
         <f t="shared" si="4"/>
-        <v>254</v>
+        <v>144</v>
       </c>
       <c r="M31">
         <f t="shared" si="5"/>
-        <v>2898</v>
+        <v>3016</v>
       </c>
       <c r="N31">
         <f t="shared" si="6"/>
-        <v>1609</v>
+        <v>260</v>
       </c>
       <c r="O31">
         <f t="shared" si="7"/>
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="P31">
         <f t="shared" si="8"/>
-        <v>254</v>
+        <v>144</v>
       </c>
       <c r="Q31">
         <f t="shared" si="9"/>
-        <v>1634</v>
+        <v>966</v>
       </c>
       <c r="R31" t="b">
         <f t="shared" si="0"/>
@@ -2287,43 +2287,43 @@
         <v>321</v>
       </c>
       <c r="F32" s="2">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="G32">
         <f t="shared" si="1"/>
-        <v>2667</v>
+        <v>3134</v>
       </c>
       <c r="H32">
         <f t="shared" si="2"/>
-        <v>1503</v>
+        <v>177</v>
       </c>
       <c r="I32">
         <f t="shared" si="3"/>
-        <v>263</v>
+        <v>321</v>
       </c>
       <c r="J32">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="M32">
         <f t="shared" si="5"/>
-        <v>2667</v>
+        <v>3134</v>
       </c>
       <c r="N32">
         <f t="shared" si="6"/>
-        <v>1503</v>
+        <v>177</v>
       </c>
       <c r="O32">
         <f t="shared" si="7"/>
-        <v>263</v>
+        <v>321</v>
       </c>
       <c r="P32">
         <f t="shared" si="8"/>
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="Q32">
         <f t="shared" si="9"/>
-        <v>1691</v>
+        <v>1099</v>
       </c>
       <c r="R32" t="b">
         <f t="shared" si="0"/>
@@ -2348,43 +2348,43 @@
         <v>194</v>
       </c>
       <c r="F33" s="2">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G33">
         <f t="shared" si="1"/>
-        <v>2662</v>
+        <v>3209</v>
       </c>
       <c r="H33">
         <f t="shared" si="2"/>
-        <v>1405</v>
+        <v>224</v>
       </c>
       <c r="I33">
         <f t="shared" si="3"/>
-        <v>306</v>
+        <v>50</v>
       </c>
       <c r="J33">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>416</v>
       </c>
       <c r="M33">
         <f t="shared" si="5"/>
-        <v>2662</v>
+        <v>3209</v>
       </c>
       <c r="N33">
         <f t="shared" si="6"/>
-        <v>1405</v>
+        <v>224</v>
       </c>
       <c r="O33">
         <f t="shared" si="7"/>
-        <v>306</v>
+        <v>50</v>
       </c>
       <c r="P33">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>416</v>
       </c>
       <c r="Q33">
         <f t="shared" si="9"/>
-        <v>1623</v>
+        <v>1162</v>
       </c>
       <c r="R33" t="b">
         <f t="shared" si="0"/>
@@ -2409,43 +2409,43 @@
         <v>327</v>
       </c>
       <c r="F34" s="2">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="G34">
         <f t="shared" si="1"/>
-        <v>2678</v>
+        <v>3562</v>
       </c>
       <c r="H34">
         <f t="shared" si="2"/>
-        <v>1417</v>
+        <v>3</v>
       </c>
       <c r="I34">
         <f t="shared" si="3"/>
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="J34">
         <f t="shared" si="4"/>
-        <v>455</v>
+        <v>64</v>
       </c>
       <c r="M34">
         <f t="shared" si="5"/>
-        <v>2678</v>
+        <v>3562</v>
       </c>
       <c r="N34">
         <f t="shared" si="6"/>
-        <v>1417</v>
+        <v>3</v>
       </c>
       <c r="O34">
         <f t="shared" si="7"/>
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="P34">
         <f t="shared" si="8"/>
-        <v>455</v>
+        <v>64</v>
       </c>
       <c r="Q34">
         <f t="shared" si="9"/>
-        <v>1620</v>
+        <v>1557</v>
       </c>
       <c r="R34" t="b">
         <f t="shared" si="0"/>
@@ -2470,43 +2470,43 @@
         <v>255</v>
       </c>
       <c r="F35" s="2">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G35">
         <f t="shared" si="1"/>
-        <v>2401</v>
+        <v>3626</v>
       </c>
       <c r="H35">
         <f t="shared" si="2"/>
-        <v>1778</v>
+        <v>4</v>
       </c>
       <c r="I35">
         <f t="shared" si="3"/>
-        <v>292</v>
+        <v>210</v>
       </c>
       <c r="J35">
         <f t="shared" si="4"/>
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="M35">
         <f t="shared" si="5"/>
-        <v>2401</v>
+        <v>3626</v>
       </c>
       <c r="N35">
         <f t="shared" si="6"/>
-        <v>1778</v>
+        <v>4</v>
       </c>
       <c r="O35">
         <f t="shared" si="7"/>
-        <v>292</v>
+        <v>210</v>
       </c>
       <c r="P35">
         <f t="shared" si="8"/>
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="Q35">
         <f t="shared" si="9"/>
-        <v>2073</v>
+        <v>1618</v>
       </c>
       <c r="R35" t="b">
         <f t="shared" ref="R35:R66" si="11">F35=""</f>
@@ -2531,43 +2531,43 @@
         <v>80</v>
       </c>
       <c r="F36" s="2">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="G36">
         <f t="shared" si="1"/>
-        <v>2286</v>
+        <v>3726</v>
       </c>
       <c r="H36">
         <f t="shared" si="2"/>
-        <v>1740</v>
+        <v>56</v>
       </c>
       <c r="I36">
         <f t="shared" si="3"/>
-        <v>307</v>
+        <v>125</v>
       </c>
       <c r="J36">
         <f t="shared" si="4"/>
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M36">
         <f t="shared" ref="M36:M67" si="12">LOOKUP($F36,$A$3:$A$202,B$3:B$202)</f>
-        <v>2286</v>
+        <v>3726</v>
       </c>
       <c r="N36">
         <f t="shared" ref="N36:N67" si="13">LOOKUP($F36,$A$3:$A$202,C$3:C$202)</f>
-        <v>1740</v>
+        <v>56</v>
       </c>
       <c r="O36">
         <f t="shared" si="7"/>
-        <v>307</v>
+        <v>125</v>
       </c>
       <c r="P36">
         <f t="shared" si="8"/>
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q36">
         <f t="shared" si="9"/>
-        <v>2126</v>
+        <v>1703</v>
       </c>
       <c r="R36" t="b">
         <f t="shared" si="11"/>
@@ -2592,43 +2592,43 @@
         <v>58</v>
       </c>
       <c r="F37" s="2">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="G37">
         <f t="shared" si="1"/>
-        <v>2133</v>
+        <v>3819</v>
       </c>
       <c r="H37">
         <f t="shared" si="2"/>
-        <v>1803</v>
+        <v>191</v>
       </c>
       <c r="I37">
         <f t="shared" si="3"/>
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="J37">
         <f t="shared" si="4"/>
-        <v>215</v>
+        <v>58</v>
       </c>
       <c r="M37">
         <f t="shared" si="12"/>
-        <v>2133</v>
+        <v>3819</v>
       </c>
       <c r="N37">
         <f t="shared" si="13"/>
-        <v>1803</v>
+        <v>191</v>
       </c>
       <c r="O37">
         <f t="shared" si="7"/>
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="P37">
         <f t="shared" si="8"/>
-        <v>215</v>
+        <v>58</v>
       </c>
       <c r="Q37">
         <f t="shared" si="9"/>
-        <v>2279</v>
+        <v>1770</v>
       </c>
       <c r="R37" t="b">
         <f t="shared" si="11"/>
@@ -2653,43 +2653,43 @@
         <v>15</v>
       </c>
       <c r="F38" s="2">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="G38">
         <f t="shared" si="1"/>
-        <v>1922</v>
+        <v>3796</v>
       </c>
       <c r="H38">
         <f t="shared" si="2"/>
-        <v>1845</v>
+        <v>244</v>
       </c>
       <c r="I38">
         <f t="shared" si="3"/>
-        <v>76</v>
+        <v>324</v>
       </c>
       <c r="J38">
         <f t="shared" si="4"/>
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="M38">
         <f t="shared" si="12"/>
-        <v>1922</v>
+        <v>3796</v>
       </c>
       <c r="N38">
         <f t="shared" si="13"/>
-        <v>1845</v>
+        <v>244</v>
       </c>
       <c r="O38">
         <f t="shared" si="7"/>
-        <v>76</v>
+        <v>324</v>
       </c>
       <c r="P38">
         <f t="shared" si="8"/>
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="Q38">
         <f t="shared" si="9"/>
-        <v>2465</v>
+        <v>1741</v>
       </c>
       <c r="R38" t="b">
         <f t="shared" si="11"/>
@@ -2714,43 +2714,43 @@
         <v>35</v>
       </c>
       <c r="F39" s="2">
-        <v>183</v>
+        <v>13</v>
       </c>
       <c r="G39">
         <f t="shared" si="1"/>
-        <v>1838</v>
+        <v>3741</v>
       </c>
       <c r="H39">
         <f t="shared" si="2"/>
-        <v>1943</v>
+        <v>252</v>
       </c>
       <c r="I39">
         <f t="shared" si="3"/>
-        <v>279</v>
+        <v>94</v>
       </c>
       <c r="J39">
         <f t="shared" si="4"/>
-        <v>234</v>
+        <v>84</v>
       </c>
       <c r="M39">
         <f t="shared" si="12"/>
-        <v>1838</v>
+        <v>3741</v>
       </c>
       <c r="N39">
         <f t="shared" si="13"/>
-        <v>1943</v>
+        <v>252</v>
       </c>
       <c r="O39">
         <f t="shared" si="7"/>
-        <v>279</v>
+        <v>94</v>
       </c>
       <c r="P39">
         <f t="shared" si="8"/>
-        <v>234</v>
+        <v>84</v>
       </c>
       <c r="Q39">
         <f t="shared" si="9"/>
-        <v>2592</v>
+        <v>1685</v>
       </c>
       <c r="R39" t="b">
         <f t="shared" si="11"/>
@@ -2775,43 +2775,43 @@
         <v>34</v>
       </c>
       <c r="F40" s="2">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G40">
         <f t="shared" si="1"/>
-        <v>1842</v>
+        <v>3697</v>
       </c>
       <c r="H40">
         <f t="shared" si="2"/>
-        <v>1709</v>
+        <v>324</v>
       </c>
       <c r="I40">
         <f t="shared" si="3"/>
-        <v>144</v>
+        <v>327</v>
       </c>
       <c r="J40">
         <f t="shared" si="4"/>
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="M40">
         <f t="shared" si="12"/>
-        <v>1842</v>
+        <v>3697</v>
       </c>
       <c r="N40">
         <f t="shared" si="13"/>
-        <v>1709</v>
+        <v>324</v>
       </c>
       <c r="O40">
         <f t="shared" si="7"/>
-        <v>144</v>
+        <v>327</v>
       </c>
       <c r="P40">
         <f t="shared" si="8"/>
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="Q40">
         <f t="shared" si="9"/>
-        <v>2442</v>
+        <v>1635</v>
       </c>
       <c r="R40" t="b">
         <f t="shared" si="11"/>
@@ -2836,43 +2836,43 @@
         <v>7</v>
       </c>
       <c r="F41" s="2">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="G41">
         <f t="shared" si="1"/>
-        <v>2005</v>
+        <v>3779</v>
       </c>
       <c r="H41">
         <f t="shared" si="2"/>
-        <v>1631</v>
+        <v>320</v>
       </c>
       <c r="I41">
         <f t="shared" si="3"/>
-        <v>292</v>
+        <v>6</v>
       </c>
       <c r="J41">
         <f t="shared" si="4"/>
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="M41">
         <f t="shared" si="12"/>
-        <v>2005</v>
+        <v>3779</v>
       </c>
       <c r="N41">
         <f t="shared" si="13"/>
-        <v>1631</v>
+        <v>320</v>
       </c>
       <c r="O41">
         <f t="shared" si="7"/>
-        <v>292</v>
+        <v>6</v>
       </c>
       <c r="P41">
         <f t="shared" si="8"/>
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="Q41">
         <f t="shared" si="9"/>
-        <v>2265</v>
+        <v>1718</v>
       </c>
       <c r="R41" t="b">
         <f t="shared" si="11"/>
@@ -2897,43 +2897,43 @@
         <v>231</v>
       </c>
       <c r="F42" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G42">
         <f t="shared" si="1"/>
-        <v>2121</v>
+        <v>3848</v>
       </c>
       <c r="H42">
         <f t="shared" si="2"/>
-        <v>1641</v>
+        <v>355</v>
       </c>
       <c r="I42">
         <f t="shared" si="3"/>
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="J42">
         <f t="shared" si="4"/>
-        <v>320</v>
+        <v>195</v>
       </c>
       <c r="M42">
         <f t="shared" si="12"/>
-        <v>2121</v>
+        <v>3848</v>
       </c>
       <c r="N42">
         <f t="shared" si="13"/>
-        <v>1641</v>
+        <v>355</v>
       </c>
       <c r="O42">
         <f t="shared" si="7"/>
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="P42">
         <f t="shared" si="8"/>
-        <v>320</v>
+        <v>195</v>
       </c>
       <c r="Q42">
         <f t="shared" si="9"/>
-        <v>2181</v>
+        <v>1785</v>
       </c>
       <c r="R42" t="b">
         <f t="shared" si="11"/>
@@ -2958,43 +2958,43 @@
         <v>195</v>
       </c>
       <c r="F43" s="2">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="G43">
         <f t="shared" si="1"/>
-        <v>2428</v>
+        <v>3735</v>
       </c>
       <c r="H43">
         <f t="shared" si="2"/>
-        <v>1551</v>
+        <v>514</v>
       </c>
       <c r="I43">
         <f t="shared" si="3"/>
-        <v>170</v>
+        <v>317</v>
       </c>
       <c r="J43">
         <f t="shared" si="4"/>
-        <v>354</v>
+        <v>230</v>
       </c>
       <c r="M43">
         <f t="shared" si="12"/>
-        <v>2428</v>
+        <v>3735</v>
       </c>
       <c r="N43">
         <f t="shared" si="13"/>
-        <v>1551</v>
+        <v>514</v>
       </c>
       <c r="O43">
         <f t="shared" si="7"/>
-        <v>170</v>
+        <v>317</v>
       </c>
       <c r="P43">
         <f t="shared" si="8"/>
-        <v>354</v>
+        <v>230</v>
       </c>
       <c r="Q43">
         <f t="shared" si="9"/>
-        <v>1892</v>
+        <v>1672</v>
       </c>
       <c r="R43" t="b">
         <f t="shared" si="11"/>
@@ -3019,43 +3019,43 @@
         <v>334</v>
       </c>
       <c r="F44" s="2">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="G44">
         <f t="shared" si="1"/>
-        <v>2498</v>
+        <v>3507</v>
       </c>
       <c r="H44">
         <f t="shared" si="2"/>
-        <v>1204</v>
+        <v>486</v>
       </c>
       <c r="I44">
         <f t="shared" si="3"/>
-        <v>107</v>
+        <v>292</v>
       </c>
       <c r="J44">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="M44">
         <f t="shared" si="12"/>
-        <v>2498</v>
+        <v>3507</v>
       </c>
       <c r="N44">
         <f t="shared" si="13"/>
-        <v>1204</v>
+        <v>486</v>
       </c>
       <c r="O44">
         <f t="shared" si="7"/>
-        <v>107</v>
+        <v>292</v>
       </c>
       <c r="P44">
         <f t="shared" si="8"/>
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="Q44">
         <f t="shared" si="9"/>
-        <v>1614</v>
+        <v>1443</v>
       </c>
       <c r="R44" t="b">
         <f t="shared" si="11"/>
@@ -3080,43 +3080,43 @@
         <v>59</v>
       </c>
       <c r="F45" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="G45">
         <f t="shared" si="1"/>
-        <v>2573</v>
+        <v>3399</v>
       </c>
       <c r="H45">
         <f t="shared" si="2"/>
-        <v>1231</v>
+        <v>405</v>
       </c>
       <c r="I45">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="J45">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="M45">
         <f t="shared" si="12"/>
-        <v>2573</v>
+        <v>3399</v>
       </c>
       <c r="N45">
         <f t="shared" si="13"/>
-        <v>1231</v>
+        <v>405</v>
       </c>
       <c r="O45">
         <f t="shared" si="7"/>
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="P45">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="Q45">
         <f t="shared" si="9"/>
-        <v>1572</v>
+        <v>1334</v>
       </c>
       <c r="R45" t="b">
         <f t="shared" si="11"/>
@@ -3141,43 +3141,43 @@
         <v>43</v>
       </c>
       <c r="F46" s="2">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="G46">
         <f t="shared" si="1"/>
-        <v>2578</v>
+        <v>3400</v>
       </c>
       <c r="H46">
         <f t="shared" si="2"/>
-        <v>1230</v>
+        <v>530</v>
       </c>
       <c r="I46">
         <f t="shared" si="3"/>
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="J46">
         <f t="shared" si="4"/>
-        <v>339</v>
+        <v>170</v>
       </c>
       <c r="M46">
         <f t="shared" si="12"/>
-        <v>2578</v>
+        <v>3400</v>
       </c>
       <c r="N46">
         <f t="shared" si="13"/>
-        <v>1230</v>
+        <v>530</v>
       </c>
       <c r="O46">
         <f t="shared" si="7"/>
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="P46">
         <f t="shared" si="8"/>
-        <v>339</v>
+        <v>170</v>
       </c>
       <c r="Q46">
         <f t="shared" si="9"/>
-        <v>1567</v>
+        <v>1339</v>
       </c>
       <c r="R46" t="b">
         <f t="shared" si="11"/>
@@ -3202,43 +3202,43 @@
         <v>321</v>
       </c>
       <c r="F47" s="2">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="G47">
         <f t="shared" si="1"/>
-        <v>2866</v>
+        <v>3369</v>
       </c>
       <c r="H47">
         <f t="shared" si="2"/>
-        <v>1409</v>
+        <v>697</v>
       </c>
       <c r="I47">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>255</v>
       </c>
       <c r="J47">
         <f t="shared" si="4"/>
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="M47">
         <f t="shared" si="12"/>
-        <v>2866</v>
+        <v>3369</v>
       </c>
       <c r="N47">
         <f t="shared" si="13"/>
-        <v>1409</v>
+        <v>697</v>
       </c>
       <c r="O47">
         <f t="shared" si="7"/>
-        <v>91</v>
+        <v>255</v>
       </c>
       <c r="P47">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="Q47">
         <f t="shared" si="9"/>
-        <v>1491</v>
+        <v>1331</v>
       </c>
       <c r="R47" t="b">
         <f t="shared" si="11"/>
@@ -3263,43 +3263,43 @@
         <v>11</v>
       </c>
       <c r="F48" s="2">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="G48">
         <f t="shared" si="1"/>
-        <v>2943</v>
+        <v>3430</v>
       </c>
       <c r="H48">
         <f t="shared" si="2"/>
-        <v>1341</v>
+        <v>746</v>
       </c>
       <c r="I48">
         <f t="shared" si="3"/>
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="J48">
         <f t="shared" si="4"/>
-        <v>184</v>
+        <v>261</v>
       </c>
       <c r="M48">
         <f t="shared" si="12"/>
-        <v>2943</v>
+        <v>3430</v>
       </c>
       <c r="N48">
         <f t="shared" si="13"/>
-        <v>1341</v>
+        <v>746</v>
       </c>
       <c r="O48">
         <f t="shared" si="7"/>
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="P48">
         <f t="shared" si="8"/>
-        <v>184</v>
+        <v>261</v>
       </c>
       <c r="Q48">
         <f t="shared" si="9"/>
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="R48" t="b">
         <f t="shared" si="11"/>
@@ -3324,43 +3324,43 @@
         <v>316</v>
       </c>
       <c r="F49" s="2">
-        <v>32</v>
+        <v>169</v>
       </c>
       <c r="G49">
         <f t="shared" si="1"/>
-        <v>3125</v>
+        <v>3661</v>
       </c>
       <c r="H49">
         <f t="shared" si="2"/>
-        <v>1312</v>
+        <v>867</v>
       </c>
       <c r="I49">
         <f t="shared" si="3"/>
-        <v>255</v>
+        <v>316</v>
       </c>
       <c r="J49">
         <f t="shared" si="4"/>
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M49">
         <f t="shared" si="12"/>
-        <v>3125</v>
+        <v>3661</v>
       </c>
       <c r="N49">
         <f t="shared" si="13"/>
-        <v>1312</v>
+        <v>867</v>
       </c>
       <c r="O49">
         <f t="shared" si="7"/>
-        <v>255</v>
+        <v>316</v>
       </c>
       <c r="P49">
         <f t="shared" si="8"/>
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q49">
         <f t="shared" si="9"/>
-        <v>1261</v>
+        <v>1655</v>
       </c>
       <c r="R49" t="b">
         <f t="shared" si="11"/>
@@ -3385,43 +3385,43 @@
         <v>58</v>
       </c>
       <c r="F50" s="2">
-        <v>3</v>
+        <v>196</v>
       </c>
       <c r="G50">
         <f t="shared" si="1"/>
-        <v>3131</v>
+        <v>3688</v>
       </c>
       <c r="H50">
         <f t="shared" si="2"/>
-        <v>1199</v>
+        <v>759</v>
       </c>
       <c r="I50">
         <f t="shared" si="3"/>
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="J50">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>231</v>
       </c>
       <c r="M50">
         <f t="shared" si="12"/>
-        <v>3131</v>
+        <v>3688</v>
       </c>
       <c r="N50">
         <f t="shared" si="13"/>
-        <v>1199</v>
+        <v>759</v>
       </c>
       <c r="O50">
         <f t="shared" si="7"/>
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="P50">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>231</v>
       </c>
       <c r="Q50">
         <f t="shared" si="9"/>
-        <v>1164</v>
+        <v>1656</v>
       </c>
       <c r="R50" t="b">
         <f t="shared" si="11"/>
@@ -3446,43 +3446,43 @@
         <v>168</v>
       </c>
       <c r="F51" s="2">
-        <v>178</v>
+        <v>81</v>
       </c>
       <c r="G51">
         <f t="shared" si="1"/>
-        <v>3134</v>
+        <v>3901</v>
       </c>
       <c r="H51">
         <f t="shared" si="2"/>
-        <v>1169</v>
+        <v>849</v>
       </c>
       <c r="I51">
         <f t="shared" si="3"/>
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J51">
         <f t="shared" si="4"/>
-        <v>199</v>
+        <v>62</v>
       </c>
       <c r="M51">
         <f t="shared" si="12"/>
-        <v>3134</v>
+        <v>3901</v>
       </c>
       <c r="N51">
         <f t="shared" si="13"/>
-        <v>1169</v>
+        <v>849</v>
       </c>
       <c r="O51">
         <f t="shared" si="7"/>
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P51">
         <f t="shared" si="8"/>
-        <v>199</v>
+        <v>62</v>
       </c>
       <c r="Q51">
         <f t="shared" si="9"/>
-        <v>1137</v>
+        <v>1883</v>
       </c>
       <c r="R51" t="b">
         <f t="shared" si="11"/>
@@ -3507,43 +3507,43 @@
         <v>213</v>
       </c>
       <c r="F52" s="2">
-        <v>52</v>
+        <v>187</v>
       </c>
       <c r="G52">
         <f t="shared" si="1"/>
-        <v>3166</v>
+        <v>3903</v>
       </c>
       <c r="H52">
         <f t="shared" si="2"/>
-        <v>973</v>
+        <v>911</v>
       </c>
       <c r="I52">
         <f t="shared" si="3"/>
-        <v>128</v>
+        <v>223</v>
       </c>
       <c r="J52">
         <f t="shared" si="4"/>
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="M52">
         <f t="shared" si="12"/>
-        <v>3166</v>
+        <v>3903</v>
       </c>
       <c r="N52">
         <f t="shared" si="13"/>
-        <v>973</v>
+        <v>911</v>
       </c>
       <c r="O52">
         <f t="shared" si="7"/>
-        <v>128</v>
+        <v>223</v>
       </c>
       <c r="P52">
         <f t="shared" si="8"/>
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="Q52">
         <f t="shared" si="9"/>
-        <v>964</v>
+        <v>1900</v>
       </c>
       <c r="R52" t="b">
         <f t="shared" si="11"/>
@@ -3568,43 +3568,43 @@
         <v>24</v>
       </c>
       <c r="F53" s="2">
-        <v>55</v>
+        <v>174</v>
       </c>
       <c r="G53">
         <f t="shared" si="1"/>
-        <v>3144</v>
+        <v>3797</v>
       </c>
       <c r="H53">
         <f t="shared" si="2"/>
-        <v>924</v>
+        <v>990</v>
       </c>
       <c r="I53">
         <f t="shared" si="3"/>
-        <v>49</v>
+        <v>244</v>
       </c>
       <c r="J53">
         <f t="shared" si="4"/>
-        <v>411</v>
+        <v>366</v>
       </c>
       <c r="M53">
         <f t="shared" si="12"/>
-        <v>3144</v>
+        <v>3797</v>
       </c>
       <c r="N53">
         <f t="shared" si="13"/>
-        <v>924</v>
+        <v>990</v>
       </c>
       <c r="O53">
         <f t="shared" si="7"/>
-        <v>49</v>
+        <v>244</v>
       </c>
       <c r="P53">
         <f t="shared" si="8"/>
-        <v>411</v>
+        <v>366</v>
       </c>
       <c r="Q53">
         <f t="shared" si="9"/>
-        <v>942</v>
+        <v>1820</v>
       </c>
       <c r="R53" t="b">
         <f t="shared" si="11"/>
@@ -3629,43 +3629,43 @@
         <v>336</v>
       </c>
       <c r="F54" s="2">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="G54">
         <f t="shared" si="1"/>
-        <v>2759</v>
+        <v>3991</v>
       </c>
       <c r="H54">
         <f t="shared" si="2"/>
-        <v>1067</v>
+        <v>1300</v>
       </c>
       <c r="I54">
         <f t="shared" si="3"/>
-        <v>73</v>
+        <v>294</v>
       </c>
       <c r="J54">
         <f t="shared" si="4"/>
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="M54">
         <f t="shared" si="12"/>
-        <v>2759</v>
+        <v>3991</v>
       </c>
       <c r="N54">
         <f t="shared" si="13"/>
-        <v>1067</v>
+        <v>1300</v>
       </c>
       <c r="O54">
         <f t="shared" si="7"/>
-        <v>73</v>
+        <v>294</v>
       </c>
       <c r="P54">
         <f t="shared" si="8"/>
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="Q54">
         <f t="shared" si="9"/>
-        <v>1324</v>
+        <v>2113</v>
       </c>
       <c r="R54" t="b">
         <f t="shared" si="11"/>
@@ -3690,43 +3690,43 @@
         <v>128</v>
       </c>
       <c r="F55" s="2">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="G55">
         <f t="shared" si="1"/>
-        <v>2682</v>
+        <v>3983</v>
       </c>
       <c r="H55">
         <f t="shared" si="2"/>
-        <v>984</v>
+        <v>1428</v>
       </c>
       <c r="I55">
         <f t="shared" si="3"/>
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="J55">
         <f t="shared" si="4"/>
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="M55">
         <f t="shared" si="12"/>
-        <v>2682</v>
+        <v>3983</v>
       </c>
       <c r="N55">
         <f t="shared" si="13"/>
-        <v>984</v>
+        <v>1428</v>
       </c>
       <c r="O55">
         <f t="shared" si="7"/>
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="P55">
         <f t="shared" si="8"/>
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="Q55">
         <f t="shared" si="9"/>
-        <v>1337</v>
+        <v>2162</v>
       </c>
       <c r="R55" t="b">
         <f t="shared" si="11"/>
@@ -3751,43 +3751,43 @@
         <v>198</v>
       </c>
       <c r="F56" s="2">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="G56">
         <f t="shared" si="1"/>
-        <v>2559</v>
+        <v>3990</v>
       </c>
       <c r="H56">
         <f t="shared" si="2"/>
-        <v>975</v>
+        <v>1450</v>
       </c>
       <c r="I56">
         <f t="shared" si="3"/>
-        <v>228</v>
+        <v>172</v>
       </c>
       <c r="J56">
         <f t="shared" si="4"/>
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="M56">
         <f t="shared" si="12"/>
-        <v>2559</v>
+        <v>3990</v>
       </c>
       <c r="N56">
         <f t="shared" si="13"/>
-        <v>975</v>
+        <v>1450</v>
       </c>
       <c r="O56">
         <f t="shared" si="7"/>
-        <v>228</v>
+        <v>172</v>
       </c>
       <c r="P56">
         <f t="shared" si="8"/>
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="Q56">
         <f t="shared" si="9"/>
-        <v>1437</v>
+        <v>2179</v>
       </c>
       <c r="R56" t="b">
         <f t="shared" si="11"/>
@@ -3812,43 +3812,43 @@
         <v>313</v>
       </c>
       <c r="F57" s="2">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="G57">
         <f t="shared" si="1"/>
-        <v>2337</v>
+        <v>3964</v>
       </c>
       <c r="H57">
         <f t="shared" si="2"/>
-        <v>850</v>
+        <v>1678</v>
       </c>
       <c r="I57">
         <f t="shared" si="3"/>
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="J57">
         <f t="shared" si="4"/>
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="M57">
         <f t="shared" si="12"/>
-        <v>2337</v>
+        <v>3964</v>
       </c>
       <c r="N57">
         <f t="shared" si="13"/>
-        <v>850</v>
+        <v>1678</v>
       </c>
       <c r="O57">
         <f t="shared" si="7"/>
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="P57">
         <f t="shared" si="8"/>
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="Q57">
         <f t="shared" si="9"/>
-        <v>1580</v>
+        <v>2272</v>
       </c>
       <c r="R57" t="b">
         <f t="shared" si="11"/>
@@ -3873,43 +3873,43 @@
         <v>49</v>
       </c>
       <c r="F58" s="2">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="G58">
         <f t="shared" si="1"/>
-        <v>2219</v>
+        <v>3855</v>
       </c>
       <c r="H58">
         <f t="shared" si="2"/>
-        <v>964</v>
+        <v>1808</v>
       </c>
       <c r="I58">
         <f t="shared" si="3"/>
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="J58">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="M58">
         <f t="shared" si="12"/>
-        <v>2219</v>
+        <v>3855</v>
       </c>
       <c r="N58">
         <f t="shared" si="13"/>
-        <v>964</v>
+        <v>1808</v>
       </c>
       <c r="O58">
         <f t="shared" si="7"/>
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="P58">
         <f t="shared" si="8"/>
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="Q58">
         <f t="shared" si="9"/>
-        <v>1734</v>
+        <v>2259</v>
       </c>
       <c r="R58" t="b">
         <f t="shared" si="11"/>
@@ -3934,43 +3934,43 @@
         <v>324</v>
       </c>
       <c r="F59" s="2">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="G59">
         <f t="shared" si="1"/>
-        <v>2207</v>
+        <v>3842</v>
       </c>
       <c r="H59">
         <f t="shared" si="2"/>
-        <v>907</v>
+        <v>1892</v>
       </c>
       <c r="I59">
         <f t="shared" si="3"/>
-        <v>214</v>
+        <v>325</v>
       </c>
       <c r="J59">
         <f t="shared" si="4"/>
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="M59">
         <f t="shared" si="12"/>
-        <v>2207</v>
+        <v>3842</v>
       </c>
       <c r="N59">
         <f t="shared" si="13"/>
-        <v>907</v>
+        <v>1892</v>
       </c>
       <c r="O59">
         <f t="shared" si="7"/>
-        <v>214</v>
+        <v>325</v>
       </c>
       <c r="P59">
         <f t="shared" si="8"/>
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="Q59">
         <f t="shared" si="9"/>
-        <v>1722</v>
+        <v>2301</v>
       </c>
       <c r="R59" t="b">
         <f t="shared" si="11"/>
@@ -3995,43 +3995,43 @@
         <v>7</v>
       </c>
       <c r="F60" s="2">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="G60">
         <f t="shared" si="1"/>
-        <v>2237</v>
+        <v>3650</v>
       </c>
       <c r="H60">
         <f t="shared" si="2"/>
-        <v>764</v>
+        <v>1882</v>
       </c>
       <c r="I60">
         <f t="shared" si="3"/>
-        <v>243</v>
+        <v>305</v>
       </c>
       <c r="J60">
         <f t="shared" si="4"/>
-        <v>391</v>
+        <v>236</v>
       </c>
       <c r="M60">
         <f t="shared" si="12"/>
-        <v>2237</v>
+        <v>3650</v>
       </c>
       <c r="N60">
         <f t="shared" si="13"/>
-        <v>764</v>
+        <v>1882</v>
       </c>
       <c r="O60">
         <f t="shared" si="7"/>
-        <v>243</v>
+        <v>305</v>
       </c>
       <c r="P60">
         <f t="shared" si="8"/>
-        <v>391</v>
+        <v>236</v>
       </c>
       <c r="Q60">
         <f t="shared" si="9"/>
-        <v>1643</v>
+        <v>2150</v>
       </c>
       <c r="R60" t="b">
         <f t="shared" si="11"/>
@@ -4056,43 +4056,43 @@
         <v>37</v>
       </c>
       <c r="F61" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="G61">
         <f t="shared" si="1"/>
-        <v>2571</v>
+        <v>3691</v>
       </c>
       <c r="H61">
         <f t="shared" si="2"/>
-        <v>560</v>
+        <v>1650</v>
       </c>
       <c r="I61">
         <f t="shared" si="3"/>
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="J61">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>240</v>
       </c>
       <c r="M61">
         <f t="shared" si="12"/>
-        <v>2571</v>
+        <v>3691</v>
       </c>
       <c r="N61">
         <f t="shared" si="13"/>
-        <v>560</v>
+        <v>1650</v>
       </c>
       <c r="O61">
         <f t="shared" si="7"/>
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="P61">
         <f t="shared" si="8"/>
-        <v>23</v>
+        <v>240</v>
       </c>
       <c r="Q61">
         <f t="shared" si="9"/>
-        <v>1265</v>
+        <v>2033</v>
       </c>
       <c r="R61" t="b">
         <f t="shared" si="11"/>
@@ -4117,43 +4117,43 @@
         <v>244</v>
       </c>
       <c r="F62" s="2">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="G62">
         <f t="shared" si="1"/>
-        <v>2549</v>
+        <v>3637</v>
       </c>
       <c r="H62">
         <f t="shared" si="2"/>
-        <v>554</v>
+        <v>1416</v>
       </c>
       <c r="I62">
         <f t="shared" si="3"/>
-        <v>99</v>
+        <v>231</v>
       </c>
       <c r="J62">
         <f t="shared" si="4"/>
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="M62">
         <f t="shared" si="12"/>
-        <v>2549</v>
+        <v>3637</v>
       </c>
       <c r="N62">
         <f t="shared" si="13"/>
-        <v>554</v>
+        <v>1416</v>
       </c>
       <c r="O62">
         <f t="shared" si="7"/>
-        <v>99</v>
+        <v>231</v>
       </c>
       <c r="P62">
         <f t="shared" si="8"/>
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="Q62">
         <f t="shared" si="9"/>
-        <v>1285</v>
+        <v>1856</v>
       </c>
       <c r="R62" t="b">
         <f t="shared" si="11"/>
@@ -4178,43 +4178,43 @@
         <v>328</v>
       </c>
       <c r="F63" s="2">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="G63">
         <f t="shared" si="1"/>
-        <v>2346</v>
+        <v>3576</v>
       </c>
       <c r="H63">
         <f t="shared" si="2"/>
-        <v>573</v>
+        <v>1287</v>
       </c>
       <c r="I63">
         <f t="shared" si="3"/>
-        <v>305</v>
+        <v>269</v>
       </c>
       <c r="J63">
         <f t="shared" si="4"/>
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="M63">
         <f t="shared" si="12"/>
-        <v>2346</v>
+        <v>3576</v>
       </c>
       <c r="N63">
         <f t="shared" si="13"/>
-        <v>573</v>
+        <v>1287</v>
       </c>
       <c r="O63">
         <f t="shared" si="7"/>
-        <v>305</v>
+        <v>269</v>
       </c>
       <c r="P63">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="Q63">
         <f t="shared" si="9"/>
-        <v>1487</v>
+        <v>1737</v>
       </c>
       <c r="R63" t="b">
         <f t="shared" si="11"/>
@@ -4239,43 +4239,43 @@
         <v>263</v>
       </c>
       <c r="F64" s="2">
-        <v>189</v>
+        <v>8</v>
       </c>
       <c r="G64">
         <f t="shared" si="1"/>
-        <v>2298</v>
+        <v>3474</v>
       </c>
       <c r="H64">
         <f t="shared" si="2"/>
-        <v>573</v>
+        <v>1230</v>
       </c>
       <c r="I64">
         <f t="shared" si="3"/>
-        <v>85</v>
+        <v>281</v>
       </c>
       <c r="J64">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="M64">
         <f t="shared" si="12"/>
-        <v>2298</v>
+        <v>3474</v>
       </c>
       <c r="N64">
         <f t="shared" si="13"/>
-        <v>573</v>
+        <v>1230</v>
       </c>
       <c r="O64">
         <f t="shared" si="7"/>
-        <v>85</v>
+        <v>281</v>
       </c>
       <c r="P64">
         <f t="shared" si="8"/>
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="Q64">
         <f t="shared" si="9"/>
-        <v>1534</v>
+        <v>1620</v>
       </c>
       <c r="R64" t="b">
         <f t="shared" si="11"/>
@@ -4300,43 +4300,43 @@
         <v>234</v>
       </c>
       <c r="F65" s="2">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="G65">
         <f t="shared" si="1"/>
-        <v>2246</v>
+        <v>3587</v>
       </c>
       <c r="H65">
         <f t="shared" si="2"/>
-        <v>490</v>
+        <v>1123</v>
       </c>
       <c r="I65">
         <f t="shared" si="3"/>
-        <v>261</v>
+        <v>219</v>
       </c>
       <c r="J65">
         <f t="shared" si="4"/>
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="M65">
         <f t="shared" si="12"/>
-        <v>2246</v>
+        <v>3587</v>
       </c>
       <c r="N65">
         <f t="shared" si="13"/>
-        <v>490</v>
+        <v>1123</v>
       </c>
       <c r="O65">
         <f t="shared" si="7"/>
-        <v>261</v>
+        <v>219</v>
       </c>
       <c r="P65">
         <f t="shared" si="8"/>
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="Q65">
         <f t="shared" si="9"/>
-        <v>1569</v>
+        <v>1672</v>
       </c>
       <c r="R65" t="b">
         <f t="shared" si="11"/>
@@ -4361,43 +4361,43 @@
         <v>162</v>
       </c>
       <c r="F66" s="2">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="G66">
         <f t="shared" si="1"/>
-        <v>2088</v>
+        <v>3585</v>
       </c>
       <c r="H66">
         <f t="shared" si="2"/>
-        <v>453</v>
+        <v>1109</v>
       </c>
       <c r="I66">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>195</v>
       </c>
       <c r="J66">
         <f t="shared" si="4"/>
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="M66">
         <f t="shared" si="12"/>
-        <v>2088</v>
+        <v>3585</v>
       </c>
       <c r="N66">
         <f t="shared" si="13"/>
-        <v>453</v>
+        <v>1109</v>
       </c>
       <c r="O66">
         <f t="shared" si="7"/>
-        <v>32</v>
+        <v>195</v>
       </c>
       <c r="P66">
         <f t="shared" si="8"/>
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="Q66">
         <f t="shared" si="9"/>
-        <v>1721</v>
+        <v>1665</v>
       </c>
       <c r="R66" t="b">
         <f t="shared" si="11"/>
@@ -4422,43 +4422,43 @@
         <v>292</v>
       </c>
       <c r="F67" s="2">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="G67">
         <f t="shared" si="1"/>
-        <v>2065</v>
+        <v>3469</v>
       </c>
       <c r="H67">
         <f t="shared" si="2"/>
-        <v>430</v>
+        <v>1080</v>
       </c>
       <c r="I67">
         <f t="shared" si="3"/>
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="J67">
         <f t="shared" si="4"/>
-        <v>208</v>
+        <v>305</v>
       </c>
       <c r="M67">
         <f t="shared" si="12"/>
-        <v>2065</v>
+        <v>3469</v>
       </c>
       <c r="N67">
         <f t="shared" si="13"/>
-        <v>430</v>
+        <v>1080</v>
       </c>
       <c r="O67">
         <f t="shared" si="7"/>
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="P67">
         <f t="shared" si="8"/>
-        <v>208</v>
+        <v>305</v>
       </c>
       <c r="Q67">
         <f t="shared" si="9"/>
-        <v>1741</v>
+        <v>1547</v>
       </c>
       <c r="R67" t="b">
         <f t="shared" ref="R67:R98" si="14">F67=""</f>
@@ -4483,43 +4483,43 @@
         <v>169</v>
       </c>
       <c r="F68" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="G68">
         <f t="shared" ref="G68:G131" si="15">IF(NOT(R68),M68,"")</f>
-        <v>1972</v>
+        <v>3171</v>
       </c>
       <c r="H68">
         <f t="shared" ref="H68:H131" si="16">IF(NOT(R68),N68,"")</f>
-        <v>616</v>
+        <v>1147</v>
       </c>
       <c r="I68">
         <f t="shared" ref="I68:I131" si="17">IF(NOT(R68),O68,"")</f>
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="J68">
         <f t="shared" ref="J68:J131" si="18">IF(S68,Q68,IF(NOT(R68),P68,""))</f>
-        <v>450</v>
+        <v>43</v>
       </c>
       <c r="M68">
         <f t="shared" ref="M68:M99" si="19">LOOKUP($F68,$A$3:$A$202,B$3:B$202)</f>
-        <v>1972</v>
+        <v>3171</v>
       </c>
       <c r="N68">
         <f t="shared" ref="N68:N99" si="20">LOOKUP($F68,$A$3:$A$202,C$3:C$202)</f>
-        <v>616</v>
+        <v>1147</v>
       </c>
       <c r="O68">
         <f t="shared" ref="O68:O131" si="21">LOOKUP($F68,$A$3:$A$202,D$3:D$202)</f>
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="P68">
         <f t="shared" ref="P68:P131" si="22">INT(SQRT((M68-M69)*(M68-M69)+(N68-N69)*(N68-N69)) +0.5)</f>
-        <v>450</v>
+        <v>43</v>
       </c>
       <c r="Q68">
         <f t="shared" ref="Q68:Q131" si="23">INT(SQRT((M$3-M68)*(M$3-M68)+(N$3-N68)*(N$3-N68)) +0.5)</f>
-        <v>1862</v>
+        <v>1318</v>
       </c>
       <c r="R68" t="b">
         <f t="shared" si="14"/>
@@ -4544,43 +4544,43 @@
         <v>162</v>
       </c>
       <c r="F69" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G69">
         <f t="shared" si="15"/>
-        <v>1774</v>
+        <v>3134</v>
       </c>
       <c r="H69">
         <f t="shared" si="16"/>
-        <v>1020</v>
+        <v>1169</v>
       </c>
       <c r="I69">
         <f t="shared" si="17"/>
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="J69">
         <f t="shared" si="18"/>
-        <v>169</v>
+        <v>30</v>
       </c>
       <c r="M69">
         <f t="shared" si="19"/>
-        <v>1774</v>
+        <v>3134</v>
       </c>
       <c r="N69">
         <f t="shared" si="20"/>
-        <v>1020</v>
+        <v>1169</v>
       </c>
       <c r="O69">
         <f t="shared" si="21"/>
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="P69">
         <f t="shared" si="22"/>
-        <v>169</v>
+        <v>30</v>
       </c>
       <c r="Q69">
         <f t="shared" si="23"/>
-        <v>2166</v>
+        <v>1300</v>
       </c>
       <c r="R69" t="b">
         <f t="shared" si="14"/>
@@ -4605,43 +4605,43 @@
         <v>167</v>
       </c>
       <c r="F70" s="2">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="G70">
         <f t="shared" si="15"/>
-        <v>1642</v>
+        <v>3131</v>
       </c>
       <c r="H70">
         <f t="shared" si="16"/>
-        <v>1125</v>
+        <v>1199</v>
       </c>
       <c r="I70">
         <f t="shared" si="17"/>
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="J70">
         <f t="shared" si="18"/>
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="M70">
         <f t="shared" si="19"/>
-        <v>1642</v>
+        <v>3131</v>
       </c>
       <c r="N70">
         <f t="shared" si="20"/>
-        <v>1125</v>
+        <v>1199</v>
       </c>
       <c r="O70">
         <f t="shared" si="21"/>
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="P70">
         <f t="shared" si="22"/>
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="Q70">
         <f t="shared" si="23"/>
-        <v>2327</v>
+        <v>1314</v>
       </c>
       <c r="R70" t="b">
         <f t="shared" si="14"/>
@@ -4666,43 +4666,43 @@
         <v>290</v>
       </c>
       <c r="F71" s="2">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="G71">
         <f t="shared" si="15"/>
-        <v>1521</v>
+        <v>3125</v>
       </c>
       <c r="H71">
         <f t="shared" si="16"/>
-        <v>1224</v>
+        <v>1312</v>
       </c>
       <c r="I71">
         <f t="shared" si="17"/>
-        <v>286</v>
+        <v>255</v>
       </c>
       <c r="J71">
         <f t="shared" si="18"/>
-        <v>236</v>
+        <v>133</v>
       </c>
       <c r="M71">
         <f t="shared" si="19"/>
-        <v>1521</v>
+        <v>3125</v>
       </c>
       <c r="N71">
         <f t="shared" si="20"/>
-        <v>1224</v>
+        <v>1312</v>
       </c>
       <c r="O71">
         <f t="shared" si="21"/>
-        <v>286</v>
+        <v>255</v>
       </c>
       <c r="P71">
         <f t="shared" si="22"/>
-        <v>236</v>
+        <v>133</v>
       </c>
       <c r="Q71">
         <f t="shared" si="23"/>
-        <v>2477</v>
+        <v>1379</v>
       </c>
       <c r="R71" t="b">
         <f t="shared" si="14"/>
@@ -4727,43 +4727,43 @@
         <v>320</v>
       </c>
       <c r="F72" s="2">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="G72">
         <f t="shared" si="15"/>
-        <v>1285</v>
+        <v>3226</v>
       </c>
       <c r="H72">
         <f t="shared" si="16"/>
-        <v>1233</v>
+        <v>1399</v>
       </c>
       <c r="I72">
         <f t="shared" si="17"/>
-        <v>328</v>
+        <v>283</v>
       </c>
       <c r="J72">
         <f t="shared" si="18"/>
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="M72">
         <f t="shared" si="19"/>
-        <v>1285</v>
+        <v>3226</v>
       </c>
       <c r="N72">
         <f t="shared" si="20"/>
-        <v>1233</v>
+        <v>1399</v>
       </c>
       <c r="O72">
         <f t="shared" si="21"/>
-        <v>328</v>
+        <v>283</v>
       </c>
       <c r="P72">
         <f t="shared" si="22"/>
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="Q72">
         <f t="shared" si="23"/>
-        <v>2699</v>
+        <v>1512</v>
       </c>
       <c r="R72" t="b">
         <f t="shared" si="14"/>
@@ -4788,43 +4788,43 @@
         <v>240</v>
       </c>
       <c r="F73" s="2">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="G73">
         <f t="shared" si="15"/>
-        <v>1229</v>
+        <v>3088</v>
       </c>
       <c r="H73">
         <f t="shared" si="16"/>
-        <v>1036</v>
+        <v>1482</v>
       </c>
       <c r="I73">
         <f t="shared" si="17"/>
-        <v>337</v>
+        <v>61</v>
       </c>
       <c r="J73">
         <f t="shared" si="18"/>
-        <v>405</v>
+        <v>169</v>
       </c>
       <c r="M73">
         <f t="shared" si="19"/>
-        <v>1229</v>
+        <v>3088</v>
       </c>
       <c r="N73">
         <f t="shared" si="20"/>
-        <v>1036</v>
+        <v>1482</v>
       </c>
       <c r="O73">
         <f t="shared" si="21"/>
-        <v>337</v>
+        <v>61</v>
       </c>
       <c r="P73">
         <f t="shared" si="22"/>
-        <v>405</v>
+        <v>169</v>
       </c>
       <c r="Q73">
         <f t="shared" si="23"/>
-        <v>2686</v>
+        <v>1467</v>
       </c>
       <c r="R73" t="b">
         <f t="shared" si="14"/>
@@ -4849,43 +4849,43 @@
         <v>204</v>
       </c>
       <c r="F74" s="2">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="G74">
         <f t="shared" si="15"/>
-        <v>883</v>
+        <v>2935</v>
       </c>
       <c r="H74">
         <f t="shared" si="16"/>
-        <v>826</v>
+        <v>1553</v>
       </c>
       <c r="I74">
         <f t="shared" si="17"/>
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="J74">
         <f t="shared" si="18"/>
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="M74">
         <f t="shared" si="19"/>
-        <v>883</v>
+        <v>2935</v>
       </c>
       <c r="N74">
         <f t="shared" si="20"/>
-        <v>826</v>
+        <v>1553</v>
       </c>
       <c r="O74">
         <f t="shared" si="21"/>
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="P74">
         <f t="shared" si="22"/>
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Q74">
         <f t="shared" si="23"/>
-        <v>2971</v>
+        <v>1421</v>
       </c>
       <c r="R74" t="b">
         <f t="shared" si="14"/>
@@ -4910,43 +4910,43 @@
         <v>337</v>
       </c>
       <c r="F75" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="G75">
         <f t="shared" si="15"/>
-        <v>849</v>
+        <v>2898</v>
       </c>
       <c r="H75">
         <f t="shared" si="16"/>
-        <v>777</v>
+        <v>1609</v>
       </c>
       <c r="I75">
         <f t="shared" si="17"/>
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="J75">
         <f t="shared" si="18"/>
-        <v>87</v>
+        <v>254</v>
       </c>
       <c r="M75">
         <f t="shared" si="19"/>
-        <v>849</v>
+        <v>2898</v>
       </c>
       <c r="N75">
         <f t="shared" si="20"/>
-        <v>777</v>
+        <v>1609</v>
       </c>
       <c r="O75">
         <f t="shared" si="21"/>
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="P75">
         <f t="shared" si="22"/>
-        <v>87</v>
+        <v>254</v>
       </c>
       <c r="Q75">
         <f t="shared" si="23"/>
-        <v>2995</v>
+        <v>1444</v>
       </c>
       <c r="R75" t="b">
         <f t="shared" si="14"/>
@@ -4971,43 +4971,43 @@
         <v>89</v>
       </c>
       <c r="F76" s="2">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="G76">
         <f t="shared" si="15"/>
-        <v>816</v>
+        <v>2667</v>
       </c>
       <c r="H76">
         <f t="shared" si="16"/>
-        <v>696</v>
+        <v>1503</v>
       </c>
       <c r="I76">
         <f t="shared" si="17"/>
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="J76">
         <f t="shared" si="18"/>
-        <v>259</v>
+        <v>87</v>
       </c>
       <c r="M76">
         <f t="shared" si="19"/>
-        <v>816</v>
+        <v>2667</v>
       </c>
       <c r="N76">
         <f t="shared" si="20"/>
-        <v>696</v>
+        <v>1503</v>
       </c>
       <c r="O76">
         <f t="shared" si="21"/>
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="P76">
         <f t="shared" si="22"/>
-        <v>259</v>
+        <v>87</v>
       </c>
       <c r="Q76">
         <f t="shared" si="23"/>
-        <v>3014</v>
+        <v>1230</v>
       </c>
       <c r="R76" t="b">
         <f t="shared" si="14"/>
@@ -5032,43 +5032,43 @@
         <v>165</v>
       </c>
       <c r="F77" s="2">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="G77">
         <f t="shared" si="15"/>
-        <v>594</v>
+        <v>2678</v>
       </c>
       <c r="H77">
         <f t="shared" si="16"/>
-        <v>563</v>
+        <v>1417</v>
       </c>
       <c r="I77">
         <f t="shared" si="17"/>
-        <v>299</v>
+        <v>234</v>
       </c>
       <c r="J77">
         <f t="shared" si="18"/>
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="M77">
         <f t="shared" si="19"/>
-        <v>594</v>
+        <v>2678</v>
       </c>
       <c r="N77">
         <f t="shared" si="20"/>
-        <v>563</v>
+        <v>1417</v>
       </c>
       <c r="O77">
         <f t="shared" si="21"/>
-        <v>299</v>
+        <v>234</v>
       </c>
       <c r="P77">
         <f t="shared" si="22"/>
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="Q77">
         <f t="shared" si="23"/>
-        <v>3218</v>
+        <v>1162</v>
       </c>
       <c r="R77" t="b">
         <f t="shared" si="14"/>
@@ -5093,43 +5093,43 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>184</v>
+        <v>9</v>
       </c>
       <c r="G78">
         <f t="shared" si="15"/>
-        <v>518</v>
+        <v>2662</v>
       </c>
       <c r="H78">
         <f t="shared" si="16"/>
-        <v>452</v>
+        <v>1405</v>
       </c>
       <c r="I78">
         <f t="shared" si="17"/>
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="J78">
         <f t="shared" si="18"/>
-        <v>448</v>
+        <v>276</v>
       </c>
       <c r="M78">
         <f t="shared" si="19"/>
-        <v>518</v>
+        <v>2662</v>
       </c>
       <c r="N78">
         <f t="shared" si="20"/>
-        <v>452</v>
+        <v>1405</v>
       </c>
       <c r="O78">
         <f t="shared" si="21"/>
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="P78">
         <f t="shared" si="22"/>
-        <v>448</v>
+        <v>276</v>
       </c>
       <c r="Q78">
         <f t="shared" si="23"/>
-        <v>3285</v>
+        <v>1143</v>
       </c>
       <c r="R78" t="b">
         <f t="shared" si="14"/>
@@ -5154,43 +5154,43 @@
         <v>144</v>
       </c>
       <c r="F79" s="2">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G79">
         <f t="shared" si="15"/>
-        <v>583</v>
+        <v>2428</v>
       </c>
       <c r="H79">
         <f t="shared" si="16"/>
-        <v>895</v>
+        <v>1551</v>
       </c>
       <c r="I79">
         <f t="shared" si="17"/>
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="J79">
         <f t="shared" si="18"/>
-        <v>91</v>
+        <v>229</v>
       </c>
       <c r="M79">
         <f t="shared" si="19"/>
-        <v>583</v>
+        <v>2428</v>
       </c>
       <c r="N79">
         <f t="shared" si="20"/>
-        <v>895</v>
+        <v>1551</v>
       </c>
       <c r="O79">
         <f t="shared" si="21"/>
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="P79">
         <f t="shared" si="22"/>
-        <v>91</v>
+        <v>229</v>
       </c>
       <c r="Q79">
         <f t="shared" si="23"/>
-        <v>3278</v>
+        <v>1178</v>
       </c>
       <c r="R79" t="b">
         <f t="shared" si="14"/>
@@ -5215,43 +5215,43 @@
         <v>276</v>
       </c>
       <c r="F80" s="2">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G80">
         <f t="shared" si="15"/>
-        <v>628</v>
+        <v>2401</v>
       </c>
       <c r="H80">
         <f t="shared" si="16"/>
-        <v>974</v>
+        <v>1778</v>
       </c>
       <c r="I80">
         <f t="shared" si="17"/>
-        <v>87</v>
+        <v>292</v>
       </c>
       <c r="J80">
         <f t="shared" si="18"/>
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="M80">
         <f t="shared" si="19"/>
-        <v>628</v>
+        <v>2401</v>
       </c>
       <c r="N80">
         <f t="shared" si="20"/>
-        <v>974</v>
+        <v>1778</v>
       </c>
       <c r="O80">
         <f t="shared" si="21"/>
-        <v>87</v>
+        <v>292</v>
       </c>
       <c r="P80">
         <f t="shared" si="22"/>
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="Q80">
         <f t="shared" si="23"/>
-        <v>3251</v>
+        <v>1389</v>
       </c>
       <c r="R80" t="b">
         <f t="shared" si="14"/>
@@ -5276,43 +5276,43 @@
         <v>146</v>
       </c>
       <c r="F81" s="2">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="G81">
         <f t="shared" si="15"/>
-        <v>664</v>
+        <v>2286</v>
       </c>
       <c r="H81">
         <f t="shared" si="16"/>
-        <v>1058</v>
+        <v>1740</v>
       </c>
       <c r="I81">
         <f t="shared" si="17"/>
-        <v>242</v>
+        <v>307</v>
       </c>
       <c r="J81">
         <f t="shared" si="18"/>
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="M81">
         <f t="shared" si="19"/>
-        <v>664</v>
+        <v>2286</v>
       </c>
       <c r="N81">
         <f t="shared" si="20"/>
-        <v>1058</v>
+        <v>1740</v>
       </c>
       <c r="O81">
         <f t="shared" si="21"/>
-        <v>242</v>
+        <v>307</v>
       </c>
       <c r="P81">
         <f t="shared" si="22"/>
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="Q81">
         <f t="shared" si="23"/>
-        <v>3236</v>
+        <v>1329</v>
       </c>
       <c r="R81" t="b">
         <f t="shared" si="14"/>
@@ -5337,43 +5337,43 @@
         <v>28</v>
       </c>
       <c r="F82" s="2">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="G82">
         <f t="shared" si="15"/>
-        <v>550</v>
+        <v>2133</v>
       </c>
       <c r="H82">
         <f t="shared" si="16"/>
-        <v>1241</v>
+        <v>1803</v>
       </c>
       <c r="I82">
         <f t="shared" si="17"/>
-        <v>334</v>
+        <v>110</v>
       </c>
       <c r="J82">
         <f t="shared" si="18"/>
-        <v>69</v>
+        <v>214</v>
       </c>
       <c r="M82">
         <f t="shared" si="19"/>
-        <v>550</v>
+        <v>2133</v>
       </c>
       <c r="N82">
         <f t="shared" si="20"/>
-        <v>1241</v>
+        <v>1803</v>
       </c>
       <c r="O82">
         <f t="shared" si="21"/>
-        <v>334</v>
+        <v>110</v>
       </c>
       <c r="P82">
         <f t="shared" si="22"/>
-        <v>69</v>
+        <v>214</v>
       </c>
       <c r="Q82">
         <f t="shared" si="23"/>
-        <v>3396</v>
+        <v>1375</v>
       </c>
       <c r="R82" t="b">
         <f t="shared" si="14"/>
@@ -5398,43 +5398,43 @@
         <v>64</v>
       </c>
       <c r="F83" s="2">
-        <v>193</v>
+        <v>23</v>
       </c>
       <c r="G83">
         <f t="shared" si="15"/>
-        <v>501</v>
+        <v>2005</v>
       </c>
       <c r="H83">
         <f t="shared" si="16"/>
-        <v>1290</v>
+        <v>1631</v>
       </c>
       <c r="I83">
         <f t="shared" si="17"/>
-        <v>190</v>
+        <v>292</v>
       </c>
       <c r="J83">
         <f t="shared" si="18"/>
-        <v>249</v>
+        <v>181</v>
       </c>
       <c r="M83">
         <f t="shared" si="19"/>
-        <v>501</v>
+        <v>2005</v>
       </c>
       <c r="N83">
         <f t="shared" si="20"/>
-        <v>1290</v>
+        <v>1631</v>
       </c>
       <c r="O83">
         <f t="shared" si="21"/>
-        <v>190</v>
+        <v>292</v>
       </c>
       <c r="P83">
         <f t="shared" si="22"/>
-        <v>249</v>
+        <v>181</v>
       </c>
       <c r="Q83">
         <f t="shared" si="23"/>
-        <v>3457</v>
+        <v>1202</v>
       </c>
       <c r="R83" t="b">
         <f t="shared" si="14"/>
@@ -5459,43 +5459,43 @@
         <v>168</v>
       </c>
       <c r="F84" s="2">
-        <v>191</v>
+        <v>76</v>
       </c>
       <c r="G84">
         <f t="shared" si="15"/>
-        <v>701</v>
+        <v>1842</v>
       </c>
       <c r="H84">
         <f t="shared" si="16"/>
-        <v>1438</v>
+        <v>1709</v>
       </c>
       <c r="I84">
         <f t="shared" si="17"/>
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="J84">
         <f t="shared" si="18"/>
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="M84">
         <f t="shared" si="19"/>
-        <v>701</v>
+        <v>1842</v>
       </c>
       <c r="N84">
         <f t="shared" si="20"/>
-        <v>1438</v>
+        <v>1709</v>
       </c>
       <c r="O84">
         <f t="shared" si="21"/>
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="P84">
         <f t="shared" si="22"/>
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="Q84">
         <f t="shared" si="23"/>
-        <v>3317</v>
+        <v>1298</v>
       </c>
       <c r="R84" t="b">
         <f t="shared" si="14"/>
@@ -5520,43 +5520,43 @@
         <v>343</v>
       </c>
       <c r="F85" s="2">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="G85">
         <f t="shared" si="15"/>
-        <v>772</v>
+        <v>1922</v>
       </c>
       <c r="H85">
         <f t="shared" si="16"/>
-        <v>1422</v>
+        <v>1845</v>
       </c>
       <c r="I85">
         <f t="shared" si="17"/>
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="J85">
         <f t="shared" si="18"/>
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="M85">
         <f t="shared" si="19"/>
-        <v>772</v>
+        <v>1922</v>
       </c>
       <c r="N85">
         <f t="shared" si="20"/>
-        <v>1422</v>
+        <v>1845</v>
       </c>
       <c r="O85">
         <f t="shared" si="21"/>
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="P85">
         <f t="shared" si="22"/>
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="Q85">
         <f t="shared" si="23"/>
-        <v>3245</v>
+        <v>1422</v>
       </c>
       <c r="R85" t="b">
         <f t="shared" si="14"/>
@@ -5581,43 +5581,43 @@
         <v>110</v>
       </c>
       <c r="F86" s="2">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="G86">
         <f t="shared" si="15"/>
-        <v>910</v>
+        <v>1838</v>
       </c>
       <c r="H86">
         <f t="shared" si="16"/>
-        <v>1383</v>
+        <v>1943</v>
       </c>
       <c r="I86">
         <f t="shared" si="17"/>
-        <v>171</v>
+        <v>279</v>
       </c>
       <c r="J86">
         <f t="shared" si="18"/>
-        <v>169</v>
+        <v>421</v>
       </c>
       <c r="M86">
         <f t="shared" si="19"/>
-        <v>910</v>
+        <v>1838</v>
       </c>
       <c r="N86">
         <f t="shared" si="20"/>
-        <v>1383</v>
+        <v>1943</v>
       </c>
       <c r="O86">
         <f t="shared" si="21"/>
-        <v>171</v>
+        <v>279</v>
       </c>
       <c r="P86">
         <f t="shared" si="22"/>
-        <v>169</v>
+        <v>421</v>
       </c>
       <c r="Q86">
         <f t="shared" si="23"/>
-        <v>3103</v>
+        <v>1530</v>
       </c>
       <c r="R86" t="b">
         <f t="shared" si="14"/>
@@ -5642,43 +5642,43 @@
         <v>51</v>
       </c>
       <c r="F87" s="2">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="G87">
         <f t="shared" si="15"/>
-        <v>1065</v>
+        <v>1417</v>
       </c>
       <c r="H87">
         <f t="shared" si="16"/>
-        <v>1451</v>
+        <v>1961</v>
       </c>
       <c r="I87">
         <f t="shared" si="17"/>
-        <v>316</v>
+        <v>76</v>
       </c>
       <c r="J87">
         <f t="shared" si="18"/>
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="M87">
         <f t="shared" si="19"/>
-        <v>1065</v>
+        <v>1417</v>
       </c>
       <c r="N87">
         <f t="shared" si="20"/>
-        <v>1451</v>
+        <v>1961</v>
       </c>
       <c r="O87">
         <f t="shared" si="21"/>
-        <v>316</v>
+        <v>76</v>
       </c>
       <c r="P87">
         <f t="shared" si="22"/>
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="Q87">
         <f t="shared" si="23"/>
-        <v>2986</v>
+        <v>1662</v>
       </c>
       <c r="R87" t="b">
         <f t="shared" si="14"/>
@@ -5703,43 +5703,43 @@
         <v>6</v>
       </c>
       <c r="F88" s="2">
-        <v>68</v>
+        <v>170</v>
       </c>
       <c r="G88">
         <f t="shared" si="15"/>
-        <v>922</v>
+        <v>1358</v>
       </c>
       <c r="H88">
         <f t="shared" si="16"/>
-        <v>1647</v>
+        <v>1913</v>
       </c>
       <c r="I88">
         <f t="shared" si="17"/>
-        <v>290</v>
+        <v>126</v>
       </c>
       <c r="J88">
         <f t="shared" si="18"/>
-        <v>458</v>
+        <v>117</v>
       </c>
       <c r="M88">
         <f t="shared" si="19"/>
-        <v>922</v>
+        <v>1358</v>
       </c>
       <c r="N88">
         <f t="shared" si="20"/>
-        <v>1647</v>
+        <v>1913</v>
       </c>
       <c r="O88">
         <f t="shared" si="21"/>
-        <v>290</v>
+        <v>126</v>
       </c>
       <c r="P88">
         <f t="shared" si="22"/>
-        <v>458</v>
+        <v>117</v>
       </c>
       <c r="Q88">
         <f t="shared" si="23"/>
-        <v>3198</v>
+        <v>1643</v>
       </c>
       <c r="R88" t="b">
         <f t="shared" si="14"/>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="J89">
         <f t="shared" si="18"/>
-        <v>117</v>
+        <v>451</v>
       </c>
       <c r="M89">
         <f t="shared" si="19"/>
@@ -5796,11 +5796,11 @@
       </c>
       <c r="P89">
         <f t="shared" si="22"/>
-        <v>117</v>
+        <v>451</v>
       </c>
       <c r="Q89">
         <f t="shared" si="23"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R89" t="b">
         <f t="shared" si="14"/>
@@ -5825,43 +5825,43 @@
         <v>229</v>
       </c>
       <c r="F90" s="2">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="G90">
         <f t="shared" si="15"/>
-        <v>1358</v>
+        <v>1065</v>
       </c>
       <c r="H90">
         <f t="shared" si="16"/>
-        <v>1913</v>
+        <v>1451</v>
       </c>
       <c r="I90">
         <f t="shared" si="17"/>
-        <v>126</v>
+        <v>316</v>
       </c>
       <c r="J90">
         <f t="shared" si="18"/>
-        <v>163</v>
+        <v>243</v>
       </c>
       <c r="M90">
         <f t="shared" si="19"/>
-        <v>1358</v>
+        <v>1065</v>
       </c>
       <c r="N90">
         <f t="shared" si="20"/>
-        <v>1913</v>
+        <v>1451</v>
       </c>
       <c r="O90">
         <f t="shared" si="21"/>
-        <v>126</v>
+        <v>316</v>
       </c>
       <c r="P90">
         <f t="shared" si="22"/>
-        <v>163</v>
+        <v>243</v>
       </c>
       <c r="Q90">
         <f t="shared" si="23"/>
-        <v>2955</v>
+        <v>1429</v>
       </c>
       <c r="R90" t="b">
         <f t="shared" si="14"/>
@@ -5886,43 +5886,43 @@
         <v>210</v>
       </c>
       <c r="F91" s="2">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="G91">
         <f t="shared" si="15"/>
-        <v>1199</v>
+        <v>922</v>
       </c>
       <c r="H91">
         <f t="shared" si="16"/>
-        <v>1948</v>
+        <v>1647</v>
       </c>
       <c r="I91">
         <f t="shared" si="17"/>
-        <v>136</v>
+        <v>290</v>
       </c>
       <c r="J91">
         <f t="shared" si="18"/>
-        <v>260</v>
+        <v>315</v>
       </c>
       <c r="M91">
         <f t="shared" si="19"/>
-        <v>1199</v>
+        <v>922</v>
       </c>
       <c r="N91">
         <f t="shared" si="20"/>
-        <v>1948</v>
+        <v>1647</v>
       </c>
       <c r="O91">
         <f t="shared" si="21"/>
-        <v>136</v>
+        <v>290</v>
       </c>
       <c r="P91">
         <f t="shared" si="22"/>
-        <v>260</v>
+        <v>315</v>
       </c>
       <c r="Q91">
         <f t="shared" si="23"/>
-        <v>3106</v>
+        <v>1670</v>
       </c>
       <c r="R91" t="b">
         <f t="shared" si="14"/>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="Q92">
         <f t="shared" si="23"/>
-        <v>3334</v>
+        <v>1901</v>
       </c>
       <c r="R92" t="b">
         <f t="shared" si="14"/>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="Q93">
         <f t="shared" si="23"/>
-        <v>3384</v>
+        <v>1924</v>
       </c>
       <c r="R93" t="b">
         <f t="shared" si="14"/>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="J94">
         <f t="shared" si="18"/>
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="M94">
         <f t="shared" si="19"/>
@@ -6101,11 +6101,11 @@
       </c>
       <c r="P94">
         <f t="shared" si="22"/>
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="Q94">
         <f t="shared" si="23"/>
-        <v>3451</v>
+        <v>1961</v>
       </c>
       <c r="R94" t="b">
         <f t="shared" si="14"/>
@@ -6130,43 +6130,43 @@
         <v>91</v>
       </c>
       <c r="F95" s="2">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="G95">
         <f t="shared" si="15"/>
-        <v>554</v>
+        <v>535</v>
       </c>
       <c r="H95">
         <f t="shared" si="16"/>
-        <v>1946</v>
+        <v>1791</v>
       </c>
       <c r="I95">
         <f t="shared" si="17"/>
-        <v>167</v>
+        <v>308</v>
       </c>
       <c r="J95">
         <f t="shared" si="18"/>
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="M95">
         <f t="shared" si="19"/>
-        <v>554</v>
+        <v>535</v>
       </c>
       <c r="N95">
         <f t="shared" si="20"/>
-        <v>1946</v>
+        <v>1791</v>
       </c>
       <c r="O95">
         <f t="shared" si="21"/>
-        <v>167</v>
+        <v>308</v>
       </c>
       <c r="P95">
         <f t="shared" si="22"/>
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="Q95">
         <f t="shared" si="23"/>
-        <v>3662</v>
+        <v>2048</v>
       </c>
       <c r="R95" t="b">
         <f t="shared" si="14"/>
@@ -6191,43 +6191,43 @@
         <v>146</v>
       </c>
       <c r="F96" s="2">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="G96">
         <f t="shared" si="15"/>
-        <v>389</v>
+        <v>554</v>
       </c>
       <c r="H96">
         <f t="shared" si="16"/>
-        <v>1979</v>
+        <v>1946</v>
       </c>
       <c r="I96">
         <f t="shared" si="17"/>
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="J96">
         <f t="shared" si="18"/>
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="M96">
         <f t="shared" si="19"/>
-        <v>389</v>
+        <v>554</v>
       </c>
       <c r="N96">
         <f t="shared" si="20"/>
-        <v>1979</v>
+        <v>1946</v>
       </c>
       <c r="O96">
         <f t="shared" si="21"/>
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="P96">
         <f t="shared" si="22"/>
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="Q96">
         <f t="shared" si="23"/>
-        <v>3823</v>
+        <v>2140</v>
       </c>
       <c r="R96" t="b">
         <f t="shared" si="14"/>
@@ -6252,43 +6252,43 @@
         <v>243</v>
       </c>
       <c r="F97" s="2">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="G97">
         <f t="shared" si="15"/>
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="H97">
         <f t="shared" si="16"/>
-        <v>1840</v>
+        <v>1979</v>
       </c>
       <c r="I97">
         <f t="shared" si="17"/>
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="J97">
         <f t="shared" si="18"/>
-        <v>183</v>
+        <v>142</v>
       </c>
       <c r="M97">
         <f t="shared" si="19"/>
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="N97">
         <f t="shared" si="20"/>
-        <v>1840</v>
+        <v>1979</v>
       </c>
       <c r="O97">
         <f t="shared" si="21"/>
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="P97">
         <f t="shared" si="22"/>
-        <v>183</v>
+        <v>142</v>
       </c>
       <c r="Q97">
         <f t="shared" si="23"/>
-        <v>3789</v>
+        <v>2282</v>
       </c>
       <c r="R97" t="b">
         <f t="shared" si="14"/>
@@ -6313,43 +6313,43 @@
         <v>125</v>
       </c>
       <c r="F98" s="2">
-        <v>163</v>
+        <v>69</v>
       </c>
       <c r="G98">
         <f t="shared" si="15"/>
-        <v>535</v>
+        <v>359</v>
       </c>
       <c r="H98">
         <f t="shared" si="16"/>
-        <v>1791</v>
+        <v>1840</v>
       </c>
       <c r="I98">
         <f t="shared" si="17"/>
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="J98">
         <f t="shared" si="18"/>
-        <v>511</v>
+        <v>130</v>
       </c>
       <c r="M98">
         <f t="shared" si="19"/>
-        <v>535</v>
+        <v>359</v>
       </c>
       <c r="N98">
         <f t="shared" si="20"/>
-        <v>1791</v>
+        <v>1840</v>
       </c>
       <c r="O98">
         <f t="shared" si="21"/>
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="P98">
         <f t="shared" si="22"/>
-        <v>511</v>
+        <v>130</v>
       </c>
       <c r="Q98">
         <f t="shared" si="23"/>
-        <v>3609</v>
+        <v>2213</v>
       </c>
       <c r="R98" t="b">
         <f t="shared" si="14"/>
@@ -6374,43 +6374,43 @@
         <v>242</v>
       </c>
       <c r="F99" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="G99">
         <f t="shared" si="15"/>
-        <v>331</v>
+        <v>229</v>
       </c>
       <c r="H99">
         <f t="shared" si="16"/>
-        <v>1322</v>
+        <v>1847</v>
       </c>
       <c r="I99">
         <f t="shared" si="17"/>
-        <v>325</v>
+        <v>153</v>
       </c>
       <c r="J99">
         <f t="shared" si="18"/>
-        <v>222</v>
+        <v>181</v>
       </c>
       <c r="M99">
         <f t="shared" si="19"/>
-        <v>331</v>
+        <v>229</v>
       </c>
       <c r="N99">
         <f t="shared" si="20"/>
-        <v>1322</v>
+        <v>1847</v>
       </c>
       <c r="O99">
         <f t="shared" si="21"/>
-        <v>325</v>
+        <v>153</v>
       </c>
       <c r="P99">
         <f t="shared" si="22"/>
-        <v>222</v>
+        <v>181</v>
       </c>
       <c r="Q99">
         <f t="shared" si="23"/>
-        <v>3629</v>
+        <v>2319</v>
       </c>
       <c r="R99" t="b">
         <f t="shared" ref="R99:R130" si="25">F99=""</f>
@@ -6435,43 +6435,43 @@
         <v>98</v>
       </c>
       <c r="F100" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G100">
         <f t="shared" si="15"/>
-        <v>189</v>
+        <v>262</v>
       </c>
       <c r="H100">
         <f t="shared" si="16"/>
-        <v>1151</v>
+        <v>1669</v>
       </c>
       <c r="I100">
         <f t="shared" si="17"/>
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="J100">
         <f t="shared" si="18"/>
-        <v>129</v>
+        <v>354</v>
       </c>
       <c r="M100">
         <f t="shared" ref="M100:M120" si="26">LOOKUP($F100,$A$3:$A$202,B$3:B$202)</f>
-        <v>189</v>
+        <v>262</v>
       </c>
       <c r="N100">
         <f t="shared" ref="N100:N120" si="27">LOOKUP($F100,$A$3:$A$202,C$3:C$202)</f>
-        <v>1151</v>
+        <v>1669</v>
       </c>
       <c r="O100">
         <f t="shared" si="21"/>
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="P100">
         <f t="shared" si="22"/>
-        <v>129</v>
+        <v>354</v>
       </c>
       <c r="Q100">
         <f t="shared" si="23"/>
-        <v>3719</v>
+        <v>2188</v>
       </c>
       <c r="R100" t="b">
         <f t="shared" si="25"/>
@@ -6496,43 +6496,43 @@
         <v>46</v>
       </c>
       <c r="F101" s="2">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="G101">
         <f t="shared" si="15"/>
-        <v>60</v>
+        <v>331</v>
       </c>
       <c r="H101">
         <f t="shared" si="16"/>
-        <v>1148</v>
+        <v>1322</v>
       </c>
       <c r="I101">
         <f t="shared" si="17"/>
-        <v>241</v>
+        <v>325</v>
       </c>
       <c r="J101">
         <f t="shared" si="18"/>
-        <v>97</v>
+        <v>173</v>
       </c>
       <c r="M101">
         <f t="shared" si="26"/>
-        <v>60</v>
+        <v>331</v>
       </c>
       <c r="N101">
         <f t="shared" si="27"/>
-        <v>1148</v>
+        <v>1322</v>
       </c>
       <c r="O101">
         <f t="shared" si="21"/>
-        <v>241</v>
+        <v>325</v>
       </c>
       <c r="P101">
         <f t="shared" si="22"/>
-        <v>97</v>
+        <v>173</v>
       </c>
       <c r="Q101">
         <f t="shared" si="23"/>
-        <v>3844</v>
+        <v>1950</v>
       </c>
       <c r="R101" t="b">
         <f t="shared" si="25"/>
@@ -6557,43 +6557,43 @@
         <v>261</v>
       </c>
       <c r="F102" s="2">
-        <v>103</v>
+        <v>193</v>
       </c>
       <c r="G102">
         <f t="shared" si="15"/>
-        <v>11</v>
+        <v>501</v>
       </c>
       <c r="H102">
         <f t="shared" si="16"/>
-        <v>1064</v>
+        <v>1290</v>
       </c>
       <c r="I102">
         <f t="shared" si="17"/>
-        <v>340</v>
+        <v>190</v>
       </c>
       <c r="J102">
         <f t="shared" si="18"/>
-        <v>428</v>
+        <v>69</v>
       </c>
       <c r="M102">
         <f t="shared" si="26"/>
-        <v>11</v>
+        <v>501</v>
       </c>
       <c r="N102">
         <f t="shared" si="27"/>
-        <v>1064</v>
+        <v>1290</v>
       </c>
       <c r="O102">
         <f t="shared" si="21"/>
-        <v>340</v>
+        <v>190</v>
       </c>
       <c r="P102">
         <f t="shared" si="22"/>
-        <v>428</v>
+        <v>69</v>
       </c>
       <c r="Q102">
         <f t="shared" si="23"/>
-        <v>3873</v>
+        <v>1785</v>
       </c>
       <c r="R102" t="b">
         <f t="shared" si="25"/>
@@ -6618,43 +6618,43 @@
         <v>159</v>
       </c>
       <c r="F103" s="2">
-        <v>192</v>
+        <v>41</v>
       </c>
       <c r="G103">
         <f t="shared" si="15"/>
-        <v>350</v>
+        <v>550</v>
       </c>
       <c r="H103">
         <f t="shared" si="16"/>
-        <v>802</v>
+        <v>1241</v>
       </c>
       <c r="I103">
         <f t="shared" si="17"/>
-        <v>217</v>
+        <v>334</v>
       </c>
       <c r="J103">
         <f t="shared" si="18"/>
-        <v>138</v>
+        <v>216</v>
       </c>
       <c r="M103">
         <f t="shared" si="26"/>
-        <v>350</v>
+        <v>550</v>
       </c>
       <c r="N103">
         <f t="shared" si="27"/>
-        <v>802</v>
+        <v>1241</v>
       </c>
       <c r="O103">
         <f t="shared" si="21"/>
-        <v>217</v>
+        <v>334</v>
       </c>
       <c r="P103">
         <f t="shared" si="22"/>
-        <v>138</v>
+        <v>216</v>
       </c>
       <c r="Q103">
         <f t="shared" si="23"/>
-        <v>3491</v>
+        <v>1718</v>
       </c>
       <c r="R103" t="b">
         <f t="shared" si="25"/>
@@ -6679,43 +6679,43 @@
         <v>325</v>
       </c>
       <c r="F104" s="2">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="G104">
         <f t="shared" si="15"/>
-        <v>307</v>
+        <v>664</v>
       </c>
       <c r="H104">
         <f t="shared" si="16"/>
-        <v>671</v>
+        <v>1058</v>
       </c>
       <c r="I104">
         <f t="shared" si="17"/>
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="J104">
         <f t="shared" si="18"/>
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="M104">
         <f t="shared" si="26"/>
-        <v>307</v>
+        <v>664</v>
       </c>
       <c r="N104">
         <f t="shared" si="27"/>
-        <v>671</v>
+        <v>1058</v>
       </c>
       <c r="O104">
         <f t="shared" si="21"/>
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="P104">
         <f t="shared" si="22"/>
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="Q104">
         <f t="shared" si="23"/>
-        <v>3515</v>
+        <v>1535</v>
       </c>
       <c r="R104" t="b">
         <f t="shared" si="25"/>
@@ -6740,43 +6740,43 @@
         <v>91</v>
       </c>
       <c r="F105" s="2">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="G105">
         <f t="shared" si="15"/>
-        <v>227</v>
+        <v>628</v>
       </c>
       <c r="H105">
         <f t="shared" si="16"/>
-        <v>534</v>
+        <v>974</v>
       </c>
       <c r="I105">
         <f t="shared" si="17"/>
-        <v>168</v>
+        <v>87</v>
       </c>
       <c r="J105">
         <f t="shared" si="18"/>
-        <v>180</v>
+        <v>91</v>
       </c>
       <c r="M105">
         <f t="shared" si="26"/>
-        <v>227</v>
+        <v>628</v>
       </c>
       <c r="N105">
         <f t="shared" si="27"/>
-        <v>534</v>
+        <v>974</v>
       </c>
       <c r="O105">
         <f t="shared" si="21"/>
-        <v>168</v>
+        <v>87</v>
       </c>
       <c r="P105">
         <f t="shared" si="22"/>
-        <v>180</v>
+        <v>91</v>
       </c>
       <c r="Q105">
         <f t="shared" si="23"/>
-        <v>3581</v>
+        <v>1537</v>
       </c>
       <c r="R105" t="b">
         <f t="shared" si="25"/>
@@ -6801,43 +6801,43 @@
         <v>340</v>
       </c>
       <c r="F106" s="2">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G106">
         <f t="shared" si="15"/>
-        <v>97</v>
+        <v>583</v>
       </c>
       <c r="H106">
         <f t="shared" si="16"/>
-        <v>409</v>
+        <v>895</v>
       </c>
       <c r="I106">
         <f t="shared" si="17"/>
-        <v>194</v>
+        <v>59</v>
       </c>
       <c r="J106">
         <f t="shared" si="18"/>
-        <v>68</v>
+        <v>251</v>
       </c>
       <c r="M106">
         <f t="shared" si="26"/>
-        <v>97</v>
+        <v>583</v>
       </c>
       <c r="N106">
         <f t="shared" si="27"/>
-        <v>409</v>
+        <v>895</v>
       </c>
       <c r="O106">
         <f t="shared" si="21"/>
-        <v>194</v>
+        <v>59</v>
       </c>
       <c r="P106">
         <f t="shared" si="22"/>
-        <v>68</v>
+        <v>251</v>
       </c>
       <c r="Q106">
         <f t="shared" si="23"/>
-        <v>3703</v>
+        <v>1553</v>
       </c>
       <c r="R106" t="b">
         <f t="shared" si="25"/>
@@ -6862,43 +6862,43 @@
         <v>84</v>
       </c>
       <c r="F107" s="2">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="G107">
         <f t="shared" si="15"/>
-        <v>165</v>
+        <v>350</v>
       </c>
       <c r="H107">
         <f t="shared" si="16"/>
-        <v>413</v>
+        <v>802</v>
       </c>
       <c r="I107">
         <f t="shared" si="17"/>
-        <v>313</v>
+        <v>217</v>
       </c>
       <c r="J107">
         <f t="shared" si="18"/>
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="M107">
         <f t="shared" si="26"/>
-        <v>165</v>
+        <v>350</v>
       </c>
       <c r="N107">
         <f t="shared" si="27"/>
-        <v>413</v>
+        <v>802</v>
       </c>
       <c r="O107">
         <f t="shared" si="21"/>
-        <v>313</v>
+        <v>217</v>
       </c>
       <c r="P107">
         <f t="shared" si="22"/>
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="Q107">
         <f t="shared" si="23"/>
-        <v>3635</v>
+        <v>1755</v>
       </c>
       <c r="R107" t="b">
         <f t="shared" si="25"/>
@@ -6923,43 +6923,43 @@
         <v>156</v>
       </c>
       <c r="F108" s="2">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="G108">
         <f t="shared" si="15"/>
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="H108">
         <f t="shared" si="16"/>
-        <v>362</v>
+        <v>671</v>
       </c>
       <c r="I108">
         <f t="shared" si="17"/>
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="J108">
         <f t="shared" si="18"/>
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="M108">
         <f t="shared" si="26"/>
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="N108">
         <f t="shared" si="27"/>
-        <v>362</v>
+        <v>671</v>
       </c>
       <c r="O108">
         <f t="shared" si="21"/>
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="P108">
         <f t="shared" si="22"/>
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="Q108">
         <f t="shared" si="23"/>
-        <v>3536</v>
+        <v>1774</v>
       </c>
       <c r="R108" t="b">
         <f t="shared" si="25"/>
@@ -6984,43 +6984,43 @@
         <v>41</v>
       </c>
       <c r="F109" s="2">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="G109">
         <f t="shared" si="15"/>
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="H109">
         <f t="shared" si="16"/>
-        <v>318</v>
+        <v>534</v>
       </c>
       <c r="I109">
         <f t="shared" si="17"/>
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="J109">
         <f t="shared" si="18"/>
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="M109">
         <f t="shared" si="26"/>
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="N109">
         <f t="shared" si="27"/>
-        <v>318</v>
+        <v>534</v>
       </c>
       <c r="O109">
         <f t="shared" si="21"/>
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="P109">
         <f t="shared" si="22"/>
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="Q109">
         <f t="shared" si="23"/>
-        <v>3519</v>
+        <v>1841</v>
       </c>
       <c r="R109" t="b">
         <f t="shared" si="25"/>
@@ -7045,43 +7045,43 @@
         <v>342</v>
       </c>
       <c r="F110" s="2">
-        <v>177</v>
+        <v>30</v>
       </c>
       <c r="G110">
         <f t="shared" si="15"/>
-        <v>263</v>
+        <v>97</v>
       </c>
       <c r="H110">
         <f t="shared" si="16"/>
-        <v>208</v>
+        <v>409</v>
       </c>
       <c r="I110">
         <f t="shared" si="17"/>
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="J110">
         <f t="shared" si="18"/>
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="M110">
         <f t="shared" si="26"/>
-        <v>263</v>
+        <v>97</v>
       </c>
       <c r="N110">
         <f t="shared" si="27"/>
-        <v>208</v>
+        <v>409</v>
       </c>
       <c r="O110">
         <f t="shared" si="21"/>
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="P110">
         <f t="shared" si="22"/>
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="Q110">
         <f t="shared" si="23"/>
-        <v>3533</v>
+        <v>1968</v>
       </c>
       <c r="R110" t="b">
         <f t="shared" si="25"/>
@@ -7106,43 +7106,43 @@
         <v>260</v>
       </c>
       <c r="F111" s="2">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="G111">
         <f t="shared" si="15"/>
-        <v>249</v>
+        <v>165</v>
       </c>
       <c r="H111">
         <f t="shared" si="16"/>
-        <v>47</v>
+        <v>413</v>
       </c>
       <c r="I111">
         <f t="shared" si="17"/>
-        <v>235</v>
+        <v>313</v>
       </c>
       <c r="J111">
         <f t="shared" si="18"/>
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="M111">
         <f t="shared" si="26"/>
-        <v>249</v>
+        <v>165</v>
       </c>
       <c r="N111">
         <f t="shared" si="27"/>
-        <v>47</v>
+        <v>413</v>
       </c>
       <c r="O111">
         <f t="shared" si="21"/>
-        <v>235</v>
+        <v>313</v>
       </c>
       <c r="P111">
         <f t="shared" si="22"/>
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="Q111">
         <f t="shared" si="23"/>
-        <v>3552</v>
+        <v>1900</v>
       </c>
       <c r="R111" t="b">
         <f t="shared" si="25"/>
@@ -7167,43 +7167,43 @@
         <v>93</v>
       </c>
       <c r="F112" s="2">
-        <v>190</v>
+        <v>147</v>
       </c>
       <c r="G112">
         <f t="shared" si="15"/>
-        <v>373</v>
+        <v>262</v>
       </c>
       <c r="H112">
         <f t="shared" si="16"/>
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="I112">
         <f t="shared" si="17"/>
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="J112">
         <f t="shared" si="18"/>
-        <v>288</v>
+        <v>47</v>
       </c>
       <c r="M112">
         <f t="shared" si="26"/>
-        <v>373</v>
+        <v>262</v>
       </c>
       <c r="N112">
         <f t="shared" si="27"/>
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="O112">
         <f t="shared" si="21"/>
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="P112">
         <f t="shared" si="22"/>
-        <v>288</v>
+        <v>47</v>
       </c>
       <c r="Q112">
         <f t="shared" si="23"/>
-        <v>3427</v>
+        <v>1804</v>
       </c>
       <c r="R112" t="b">
         <f t="shared" si="25"/>
@@ -7228,43 +7228,43 @@
         <v>152</v>
       </c>
       <c r="F113" s="2">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="G113">
         <f t="shared" si="15"/>
-        <v>661</v>
+        <v>278</v>
       </c>
       <c r="H113">
         <f t="shared" si="16"/>
-        <v>87</v>
+        <v>318</v>
       </c>
       <c r="I113">
         <f t="shared" si="17"/>
-        <v>264</v>
+        <v>84</v>
       </c>
       <c r="J113">
         <f t="shared" si="18"/>
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="M113">
         <f t="shared" si="26"/>
-        <v>661</v>
+        <v>278</v>
       </c>
       <c r="N113">
         <f t="shared" si="27"/>
-        <v>87</v>
+        <v>318</v>
       </c>
       <c r="O113">
         <f t="shared" si="21"/>
-        <v>264</v>
+        <v>84</v>
       </c>
       <c r="P113">
         <f t="shared" si="22"/>
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="Q113">
         <f t="shared" si="23"/>
-        <v>3139</v>
+        <v>1791</v>
       </c>
       <c r="R113" t="b">
         <f t="shared" si="25"/>
@@ -7289,43 +7289,43 @@
         <v>228</v>
       </c>
       <c r="F114" s="2">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="G114">
         <f t="shared" si="15"/>
-        <v>816</v>
+        <v>263</v>
       </c>
       <c r="H114">
         <f t="shared" si="16"/>
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="I114">
         <f t="shared" si="17"/>
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="J114">
         <f t="shared" si="18"/>
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="M114">
         <f t="shared" si="26"/>
-        <v>816</v>
+        <v>263</v>
       </c>
       <c r="N114">
         <f t="shared" si="27"/>
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="O114">
         <f t="shared" si="21"/>
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="P114">
         <f t="shared" si="22"/>
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="Q114">
         <f t="shared" si="23"/>
-        <v>2984</v>
+        <v>1816</v>
       </c>
       <c r="R114" t="b">
         <f t="shared" si="25"/>
@@ -7350,43 +7350,43 @@
         <v>175</v>
       </c>
       <c r="F115" s="2">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G115">
         <f t="shared" si="15"/>
-        <v>932</v>
+        <v>249</v>
       </c>
       <c r="H115">
         <f t="shared" si="16"/>
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="I115">
         <f t="shared" si="17"/>
-        <v>120</v>
+        <v>235</v>
       </c>
       <c r="J115">
         <f t="shared" si="18"/>
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="M115">
         <f t="shared" si="26"/>
-        <v>932</v>
+        <v>249</v>
       </c>
       <c r="N115">
         <f t="shared" si="27"/>
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="O115">
         <f t="shared" si="21"/>
-        <v>120</v>
+        <v>235</v>
       </c>
       <c r="P115">
         <f t="shared" si="22"/>
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="Q115">
         <f t="shared" si="23"/>
-        <v>2872</v>
+        <v>1856</v>
       </c>
       <c r="R115" t="b">
         <f t="shared" si="25"/>
@@ -7411,43 +7411,43 @@
         <v>34</v>
       </c>
       <c r="F116" s="2">
-        <v>29</v>
+        <v>190</v>
       </c>
       <c r="G116">
         <f t="shared" si="15"/>
-        <v>990</v>
+        <v>373</v>
       </c>
       <c r="H116">
         <f t="shared" si="16"/>
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="I116">
         <f t="shared" si="17"/>
-        <v>321</v>
+        <v>250</v>
       </c>
       <c r="J116">
         <f t="shared" si="18"/>
-        <v>108</v>
+        <v>288</v>
       </c>
       <c r="M116">
         <f t="shared" si="26"/>
-        <v>990</v>
+        <v>373</v>
       </c>
       <c r="N116">
         <f t="shared" si="27"/>
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="O116">
         <f t="shared" si="21"/>
-        <v>321</v>
+        <v>250</v>
       </c>
       <c r="P116">
         <f t="shared" si="22"/>
-        <v>108</v>
+        <v>288</v>
       </c>
       <c r="Q116">
         <f t="shared" si="23"/>
-        <v>2813</v>
+        <v>1728</v>
       </c>
       <c r="R116" t="b">
         <f t="shared" si="25"/>
@@ -7472,43 +7472,43 @@
         <v>307</v>
       </c>
       <c r="F117" s="2">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="G117">
         <f t="shared" si="15"/>
-        <v>892</v>
+        <v>661</v>
       </c>
       <c r="H117">
         <f t="shared" si="16"/>
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I117">
         <f t="shared" si="17"/>
-        <v>51</v>
+        <v>264</v>
       </c>
       <c r="J117">
         <f t="shared" si="18"/>
-        <v>360</v>
+        <v>139</v>
       </c>
       <c r="M117">
         <f t="shared" si="26"/>
-        <v>892</v>
+        <v>661</v>
       </c>
       <c r="N117">
         <f t="shared" si="27"/>
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="O117">
         <f t="shared" si="21"/>
-        <v>51</v>
+        <v>264</v>
       </c>
       <c r="P117">
         <f t="shared" si="22"/>
-        <v>360</v>
+        <v>139</v>
       </c>
       <c r="Q117">
         <f t="shared" si="23"/>
-        <v>2908</v>
+        <v>1445</v>
       </c>
       <c r="R117" t="b">
         <f t="shared" si="25"/>
@@ -7533,43 +7533,43 @@
         <v>279</v>
       </c>
       <c r="F118" s="2">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="G118">
         <f t="shared" si="15"/>
-        <v>681</v>
+        <v>656</v>
       </c>
       <c r="H118">
         <f t="shared" si="16"/>
-        <v>385</v>
+        <v>226</v>
       </c>
       <c r="I118">
         <f t="shared" si="17"/>
-        <v>281</v>
+        <v>51</v>
       </c>
       <c r="J118">
         <f t="shared" si="18"/>
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="M118">
         <f t="shared" si="26"/>
-        <v>681</v>
+        <v>656</v>
       </c>
       <c r="N118">
         <f t="shared" si="27"/>
-        <v>385</v>
+        <v>226</v>
       </c>
       <c r="O118">
         <f t="shared" si="21"/>
-        <v>281</v>
+        <v>51</v>
       </c>
       <c r="P118">
         <f t="shared" si="22"/>
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="Q118">
         <f t="shared" si="23"/>
-        <v>3118</v>
+        <v>1424</v>
       </c>
       <c r="R118" t="b">
         <f t="shared" si="25"/>
@@ -7594,43 +7594,43 @@
         <v>259</v>
       </c>
       <c r="F119" s="2">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="G119">
         <f t="shared" si="15"/>
-        <v>704</v>
+        <v>681</v>
       </c>
       <c r="H119">
         <f t="shared" si="16"/>
-        <v>535</v>
+        <v>385</v>
       </c>
       <c r="I119">
         <f t="shared" si="17"/>
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="J119">
         <f t="shared" si="18"/>
-        <v>248</v>
+        <v>176</v>
       </c>
       <c r="M119">
         <f t="shared" si="26"/>
-        <v>704</v>
+        <v>681</v>
       </c>
       <c r="N119">
         <f t="shared" si="27"/>
-        <v>535</v>
+        <v>385</v>
       </c>
       <c r="O119">
         <f t="shared" si="21"/>
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="P119">
         <f t="shared" si="22"/>
-        <v>248</v>
+        <v>176</v>
       </c>
       <c r="Q119">
         <f t="shared" si="23"/>
-        <v>3106</v>
+        <v>1385</v>
       </c>
       <c r="R119" t="b">
         <f t="shared" si="25"/>
@@ -7655,43 +7655,43 @@
         <v>136</v>
       </c>
       <c r="F120" s="2">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="G120">
         <f t="shared" si="15"/>
-        <v>949</v>
+        <v>518</v>
       </c>
       <c r="H120">
         <f t="shared" si="16"/>
-        <v>576</v>
+        <v>452</v>
       </c>
       <c r="I120">
         <f t="shared" si="17"/>
-        <v>76</v>
+        <v>337</v>
       </c>
       <c r="J120">
         <f t="shared" si="18"/>
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="M120">
         <f t="shared" si="26"/>
-        <v>949</v>
+        <v>518</v>
       </c>
       <c r="N120">
         <f t="shared" si="27"/>
-        <v>576</v>
+        <v>452</v>
       </c>
       <c r="O120">
         <f t="shared" si="21"/>
-        <v>76</v>
+        <v>337</v>
       </c>
       <c r="P120">
         <f t="shared" si="22"/>
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="Q120">
         <f t="shared" si="23"/>
-        <v>2866</v>
+        <v>1547</v>
       </c>
       <c r="R120" t="b">
         <f t="shared" si="25"/>
@@ -7716,43 +7716,43 @@
         <v>337</v>
       </c>
       <c r="F121" s="2">
-        <v>149</v>
+        <v>28</v>
       </c>
       <c r="G121">
         <f t="shared" si="15"/>
-        <v>993</v>
+        <v>594</v>
       </c>
       <c r="H121">
         <f t="shared" si="16"/>
-        <v>581</v>
+        <v>563</v>
       </c>
       <c r="I121">
         <f t="shared" si="17"/>
-        <v>134</v>
+        <v>299</v>
       </c>
       <c r="J121">
         <f t="shared" si="18"/>
-        <v>188</v>
+        <v>114</v>
       </c>
       <c r="M121">
         <f t="shared" ref="M121:O184" si="28">LOOKUP($F121,$A$3:$A$202,B$3:B$202)</f>
-        <v>993</v>
+        <v>594</v>
       </c>
       <c r="N121">
         <f t="shared" si="28"/>
-        <v>581</v>
+        <v>563</v>
       </c>
       <c r="O121">
         <f t="shared" si="21"/>
-        <v>134</v>
+        <v>299</v>
       </c>
       <c r="P121">
         <f t="shared" si="22"/>
-        <v>188</v>
+        <v>114</v>
       </c>
       <c r="Q121">
         <f t="shared" si="23"/>
-        <v>2823</v>
+        <v>1477</v>
       </c>
       <c r="R121" t="b">
         <f t="shared" si="25"/>
@@ -7777,43 +7777,43 @@
         <v>219</v>
       </c>
       <c r="F122" s="2">
-        <v>47</v>
+        <v>166</v>
       </c>
       <c r="G122">
         <f t="shared" si="15"/>
-        <v>901</v>
+        <v>704</v>
       </c>
       <c r="H122">
         <f t="shared" si="16"/>
-        <v>745</v>
+        <v>535</v>
       </c>
       <c r="I122">
         <f t="shared" si="17"/>
-        <v>58</v>
+        <v>252</v>
       </c>
       <c r="J122">
         <f t="shared" si="18"/>
-        <v>46</v>
+        <v>196</v>
       </c>
       <c r="M122">
         <f t="shared" si="28"/>
-        <v>901</v>
+        <v>704</v>
       </c>
       <c r="N122">
         <f t="shared" si="28"/>
-        <v>745</v>
+        <v>535</v>
       </c>
       <c r="O122">
         <f t="shared" si="21"/>
-        <v>58</v>
+        <v>252</v>
       </c>
       <c r="P122">
         <f t="shared" si="22"/>
-        <v>46</v>
+        <v>196</v>
       </c>
       <c r="Q122">
         <f t="shared" si="23"/>
-        <v>2938</v>
+        <v>1365</v>
       </c>
       <c r="R122" t="b">
         <f t="shared" si="25"/>
@@ -7838,43 +7838,43 @@
         <v>216</v>
       </c>
       <c r="F123" s="2">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G123">
         <f t="shared" si="15"/>
-        <v>928</v>
+        <v>816</v>
       </c>
       <c r="H123">
         <f t="shared" si="16"/>
-        <v>782</v>
+        <v>696</v>
       </c>
       <c r="I123">
         <f t="shared" si="17"/>
-        <v>169</v>
+        <v>276</v>
       </c>
       <c r="J123">
         <f t="shared" si="18"/>
-        <v>287</v>
+        <v>87</v>
       </c>
       <c r="M123">
         <f t="shared" si="28"/>
-        <v>928</v>
+        <v>816</v>
       </c>
       <c r="N123">
         <f t="shared" si="28"/>
-        <v>782</v>
+        <v>696</v>
       </c>
       <c r="O123">
         <f t="shared" si="21"/>
-        <v>169</v>
+        <v>276</v>
       </c>
       <c r="P123">
         <f t="shared" si="22"/>
-        <v>287</v>
+        <v>87</v>
       </c>
       <c r="Q123">
         <f t="shared" si="23"/>
-        <v>2918</v>
+        <v>1277</v>
       </c>
       <c r="R123" t="b">
         <f t="shared" si="25"/>
@@ -7899,43 +7899,43 @@
         <v>319</v>
       </c>
       <c r="F124" s="2">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="G124">
         <f t="shared" si="15"/>
-        <v>1172</v>
+        <v>849</v>
       </c>
       <c r="H124">
         <f t="shared" si="16"/>
-        <v>933</v>
+        <v>777</v>
       </c>
       <c r="I124">
         <f t="shared" si="17"/>
-        <v>244</v>
+        <v>156</v>
       </c>
       <c r="J124">
         <f t="shared" si="18"/>
-        <v>191</v>
+        <v>61</v>
       </c>
       <c r="M124">
         <f t="shared" si="28"/>
-        <v>1172</v>
+        <v>849</v>
       </c>
       <c r="N124">
         <f t="shared" si="28"/>
-        <v>933</v>
+        <v>777</v>
       </c>
       <c r="O124">
         <f t="shared" si="21"/>
-        <v>244</v>
+        <v>156</v>
       </c>
       <c r="P124">
         <f t="shared" si="22"/>
-        <v>191</v>
+        <v>61</v>
       </c>
       <c r="Q124">
         <f t="shared" si="23"/>
-        <v>2713</v>
+        <v>1265</v>
       </c>
       <c r="R124" t="b">
         <f t="shared" si="25"/>
@@ -7960,43 +7960,43 @@
         <v>6</v>
       </c>
       <c r="F125" s="2">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="G125">
         <f t="shared" si="15"/>
-        <v>1341</v>
+        <v>901</v>
       </c>
       <c r="H125">
         <f t="shared" si="16"/>
-        <v>844</v>
+        <v>745</v>
       </c>
       <c r="I125">
         <f t="shared" si="17"/>
-        <v>337</v>
+        <v>58</v>
       </c>
       <c r="J125">
         <f t="shared" si="18"/>
-        <v>217</v>
+        <v>46</v>
       </c>
       <c r="M125">
         <f t="shared" si="28"/>
-        <v>1341</v>
+        <v>901</v>
       </c>
       <c r="N125">
         <f t="shared" si="28"/>
-        <v>844</v>
+        <v>745</v>
       </c>
       <c r="O125">
         <f t="shared" si="21"/>
-        <v>337</v>
+        <v>58</v>
       </c>
       <c r="P125">
         <f t="shared" si="22"/>
-        <v>217</v>
+        <v>46</v>
       </c>
       <c r="Q125">
         <f t="shared" si="23"/>
-        <v>2527</v>
+        <v>1206</v>
       </c>
       <c r="R125" t="b">
         <f t="shared" si="25"/>
@@ -8021,43 +8021,43 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="G126">
         <f t="shared" si="15"/>
-        <v>1410</v>
+        <v>928</v>
       </c>
       <c r="H126">
         <f t="shared" si="16"/>
-        <v>1050</v>
+        <v>782</v>
       </c>
       <c r="I126">
         <f t="shared" si="17"/>
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="J126">
         <f t="shared" si="18"/>
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M126">
         <f t="shared" si="28"/>
-        <v>1410</v>
+        <v>928</v>
       </c>
       <c r="N126">
         <f t="shared" si="28"/>
-        <v>1050</v>
+        <v>782</v>
       </c>
       <c r="O126">
         <f t="shared" si="21"/>
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="P126">
         <f t="shared" si="22"/>
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="Q126">
         <f t="shared" si="23"/>
-        <v>2518</v>
+        <v>1190</v>
       </c>
       <c r="R126" t="b">
         <f t="shared" si="25"/>
@@ -8082,43 +8082,43 @@
         <v>193</v>
       </c>
       <c r="F127" s="2">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="G127">
         <f t="shared" si="15"/>
-        <v>1479</v>
+        <v>883</v>
       </c>
       <c r="H127">
         <f t="shared" si="16"/>
-        <v>1027</v>
+        <v>826</v>
       </c>
       <c r="I127">
         <f t="shared" si="17"/>
-        <v>336</v>
+        <v>259</v>
       </c>
       <c r="J127">
         <f t="shared" si="18"/>
-        <v>478</v>
+        <v>308</v>
       </c>
       <c r="M127">
         <f t="shared" si="28"/>
-        <v>1479</v>
+        <v>883</v>
       </c>
       <c r="N127">
         <f t="shared" si="28"/>
-        <v>1027</v>
+        <v>826</v>
       </c>
       <c r="O127">
         <f t="shared" si="21"/>
-        <v>336</v>
+        <v>259</v>
       </c>
       <c r="P127">
         <f t="shared" si="22"/>
-        <v>478</v>
+        <v>308</v>
       </c>
       <c r="Q127">
         <f t="shared" si="23"/>
-        <v>2446</v>
+        <v>1247</v>
       </c>
       <c r="R127" t="b">
         <f t="shared" si="25"/>
@@ -8143,43 +8143,43 @@
         <v>25</v>
       </c>
       <c r="F128" s="2">
-        <v>162</v>
+        <v>59</v>
       </c>
       <c r="G128">
         <f t="shared" si="15"/>
-        <v>1416</v>
+        <v>1172</v>
       </c>
       <c r="H128">
         <f t="shared" si="16"/>
-        <v>553</v>
+        <v>933</v>
       </c>
       <c r="I128">
         <f t="shared" si="17"/>
-        <v>62</v>
+        <v>244</v>
       </c>
       <c r="J128">
         <f t="shared" si="18"/>
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="M128">
         <f t="shared" si="28"/>
-        <v>1416</v>
+        <v>1172</v>
       </c>
       <c r="N128">
         <f t="shared" si="28"/>
-        <v>553</v>
+        <v>933</v>
       </c>
       <c r="O128">
         <f t="shared" si="21"/>
-        <v>62</v>
+        <v>244</v>
       </c>
       <c r="P128">
         <f t="shared" si="22"/>
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="Q128">
         <f t="shared" si="23"/>
-        <v>2400</v>
+        <v>1025</v>
       </c>
       <c r="R128" t="b">
         <f t="shared" si="25"/>
@@ -8204,43 +8204,43 @@
         <v>51</v>
       </c>
       <c r="F129" s="2">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="G129">
         <f t="shared" si="15"/>
-        <v>1414</v>
+        <v>1229</v>
       </c>
       <c r="H129">
         <f t="shared" si="16"/>
-        <v>472</v>
+        <v>1036</v>
       </c>
       <c r="I129">
         <f t="shared" si="17"/>
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="J129">
         <f t="shared" si="18"/>
-        <v>523</v>
+        <v>205</v>
       </c>
       <c r="M129">
         <f t="shared" si="28"/>
-        <v>1414</v>
+        <v>1229</v>
       </c>
       <c r="N129">
         <f t="shared" si="28"/>
-        <v>472</v>
+        <v>1036</v>
       </c>
       <c r="O129">
         <f t="shared" si="21"/>
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="P129">
         <f t="shared" si="22"/>
-        <v>523</v>
+        <v>205</v>
       </c>
       <c r="Q129">
         <f t="shared" si="23"/>
-        <v>2393</v>
+        <v>1033</v>
       </c>
       <c r="R129" t="b">
         <f t="shared" si="25"/>
@@ -8265,43 +8265,43 @@
         <v>158</v>
       </c>
       <c r="F130" s="2">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="G130">
         <f t="shared" si="15"/>
-        <v>1913</v>
+        <v>1285</v>
       </c>
       <c r="H130">
         <f t="shared" si="16"/>
-        <v>314</v>
+        <v>1233</v>
       </c>
       <c r="I130">
         <f t="shared" si="17"/>
-        <v>247</v>
+        <v>328</v>
       </c>
       <c r="J130">
         <f t="shared" si="18"/>
-        <v>120</v>
+        <v>236</v>
       </c>
       <c r="M130">
         <f t="shared" si="28"/>
-        <v>1913</v>
+        <v>1285</v>
       </c>
       <c r="N130">
         <f t="shared" si="28"/>
-        <v>314</v>
+        <v>1233</v>
       </c>
       <c r="O130">
         <f t="shared" si="21"/>
-        <v>247</v>
+        <v>328</v>
       </c>
       <c r="P130">
         <f t="shared" si="22"/>
-        <v>120</v>
+        <v>236</v>
       </c>
       <c r="Q130">
         <f t="shared" si="23"/>
-        <v>1884</v>
+        <v>1119</v>
       </c>
       <c r="R130" t="b">
         <f t="shared" si="25"/>
@@ -8326,43 +8326,43 @@
         <v>73</v>
       </c>
       <c r="F131" s="2">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="G131">
         <f t="shared" si="15"/>
-        <v>1795</v>
+        <v>1521</v>
       </c>
       <c r="H131">
         <f t="shared" si="16"/>
-        <v>337</v>
+        <v>1224</v>
       </c>
       <c r="I131">
         <f t="shared" si="17"/>
-        <v>169</v>
+        <v>286</v>
       </c>
       <c r="J131">
         <f t="shared" si="18"/>
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="M131">
         <f t="shared" si="28"/>
-        <v>1795</v>
+        <v>1521</v>
       </c>
       <c r="N131">
         <f t="shared" si="28"/>
-        <v>337</v>
+        <v>1224</v>
       </c>
       <c r="O131">
         <f t="shared" si="21"/>
-        <v>169</v>
+        <v>286</v>
       </c>
       <c r="P131">
         <f t="shared" si="22"/>
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q131">
         <f t="shared" si="23"/>
-        <v>2003</v>
+        <v>962</v>
       </c>
       <c r="R131" t="b">
         <f t="shared" ref="R131:R162" si="29">F131=""</f>
@@ -8387,43 +8387,43 @@
         <v>63</v>
       </c>
       <c r="F132" s="2">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="G132">
         <f t="shared" ref="G132:G195" si="30">IF(NOT(R132),M132,"")</f>
-        <v>1748</v>
+        <v>1642</v>
       </c>
       <c r="H132">
         <f t="shared" ref="H132:H195" si="31">IF(NOT(R132),N132,"")</f>
-        <v>185</v>
+        <v>1125</v>
       </c>
       <c r="I132">
         <f t="shared" ref="I132:I195" si="32">IF(NOT(R132),O132,"")</f>
-        <v>311</v>
+        <v>162</v>
       </c>
       <c r="J132">
         <f t="shared" ref="J132:J195" si="33">IF(S132,Q132,IF(NOT(R132),P132,""))</f>
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="M132">
         <f t="shared" si="28"/>
-        <v>1748</v>
+        <v>1642</v>
       </c>
       <c r="N132">
         <f t="shared" si="28"/>
-        <v>185</v>
+        <v>1125</v>
       </c>
       <c r="O132">
         <f t="shared" si="28"/>
-        <v>311</v>
+        <v>162</v>
       </c>
       <c r="P132">
         <f t="shared" ref="P132:P195" si="34">INT(SQRT((M132-M133)*(M132-M133)+(N132-N133)*(N132-N133)) +0.5)</f>
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="Q132">
         <f t="shared" ref="Q132:Q195" si="35">INT(SQRT((M$3-M132)*(M$3-M132)+(N$3-N132)*(N$3-N132)) +0.5)</f>
-        <v>2049</v>
+        <v>814</v>
       </c>
       <c r="R132" t="b">
         <f t="shared" si="29"/>
@@ -8448,43 +8448,43 @@
         <v>214</v>
       </c>
       <c r="F133" s="2">
-        <v>154</v>
+        <v>51</v>
       </c>
       <c r="G133">
         <f t="shared" si="30"/>
-        <v>1878</v>
+        <v>1479</v>
       </c>
       <c r="H133">
         <f t="shared" si="31"/>
-        <v>234</v>
+        <v>1027</v>
       </c>
       <c r="I133">
         <f t="shared" si="32"/>
-        <v>65</v>
+        <v>336</v>
       </c>
       <c r="J133">
         <f t="shared" si="33"/>
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="M133">
         <f t="shared" si="28"/>
-        <v>1878</v>
+        <v>1479</v>
       </c>
       <c r="N133">
         <f t="shared" si="28"/>
-        <v>234</v>
+        <v>1027</v>
       </c>
       <c r="O133">
         <f t="shared" si="28"/>
-        <v>65</v>
+        <v>336</v>
       </c>
       <c r="P133">
         <f t="shared" si="34"/>
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="Q133">
         <f t="shared" si="35"/>
-        <v>1918</v>
+        <v>837</v>
       </c>
       <c r="R133" t="b">
         <f t="shared" si="29"/>
@@ -8509,43 +8509,43 @@
         <v>76</v>
       </c>
       <c r="F134" s="2">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="G134">
         <f t="shared" si="30"/>
-        <v>2032</v>
+        <v>1410</v>
       </c>
       <c r="H134">
         <f t="shared" si="31"/>
-        <v>230</v>
+        <v>1050</v>
       </c>
       <c r="I134">
         <f t="shared" si="32"/>
-        <v>315</v>
+        <v>93</v>
       </c>
       <c r="J134">
         <f t="shared" si="33"/>
-        <v>95</v>
+        <v>217</v>
       </c>
       <c r="M134">
         <f t="shared" si="28"/>
-        <v>2032</v>
+        <v>1410</v>
       </c>
       <c r="N134">
         <f t="shared" si="28"/>
-        <v>230</v>
+        <v>1050</v>
       </c>
       <c r="O134">
         <f t="shared" si="28"/>
-        <v>315</v>
+        <v>93</v>
       </c>
       <c r="P134">
         <f t="shared" si="34"/>
-        <v>95</v>
+        <v>217</v>
       </c>
       <c r="Q134">
         <f t="shared" si="35"/>
-        <v>1764</v>
+        <v>902</v>
       </c>
       <c r="R134" t="b">
         <f t="shared" si="29"/>
@@ -8570,43 +8570,43 @@
         <v>135</v>
       </c>
       <c r="F135" s="2">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="G135">
         <f t="shared" si="30"/>
-        <v>2097</v>
+        <v>1341</v>
       </c>
       <c r="H135">
         <f t="shared" si="31"/>
-        <v>299</v>
+        <v>844</v>
       </c>
       <c r="I135">
         <f t="shared" si="32"/>
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="J135">
         <f t="shared" si="33"/>
-        <v>179</v>
+        <v>301</v>
       </c>
       <c r="M135">
         <f t="shared" si="28"/>
-        <v>2097</v>
+        <v>1341</v>
       </c>
       <c r="N135">
         <f t="shared" si="28"/>
-        <v>299</v>
+        <v>844</v>
       </c>
       <c r="O135">
         <f t="shared" si="28"/>
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="P135">
         <f t="shared" si="34"/>
-        <v>179</v>
+        <v>301</v>
       </c>
       <c r="Q135">
         <f t="shared" si="35"/>
-        <v>1700</v>
+        <v>834</v>
       </c>
       <c r="R135" t="b">
         <f t="shared" si="29"/>
@@ -8631,43 +8631,43 @@
         <v>144</v>
       </c>
       <c r="F136" s="2">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="G136">
         <f t="shared" si="30"/>
-        <v>2218</v>
+        <v>1416</v>
       </c>
       <c r="H136">
         <f t="shared" si="31"/>
-        <v>431</v>
+        <v>553</v>
       </c>
       <c r="I136">
         <f t="shared" si="32"/>
-        <v>319</v>
+        <v>62</v>
       </c>
       <c r="J136">
         <f t="shared" si="33"/>
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="M136">
         <f t="shared" si="28"/>
-        <v>2218</v>
+        <v>1416</v>
       </c>
       <c r="N136">
         <f t="shared" si="28"/>
-        <v>431</v>
+        <v>553</v>
       </c>
       <c r="O136">
         <f t="shared" si="28"/>
-        <v>319</v>
+        <v>62</v>
       </c>
       <c r="P136">
         <f t="shared" si="34"/>
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="Q136">
         <f t="shared" si="35"/>
-        <v>1589</v>
+        <v>661</v>
       </c>
       <c r="R136" t="b">
         <f t="shared" si="29"/>
@@ -8692,43 +8692,43 @@
         <v>55</v>
       </c>
       <c r="F137" s="2">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="G137">
         <f t="shared" si="30"/>
-        <v>2371</v>
+        <v>1414</v>
       </c>
       <c r="H137">
         <f t="shared" si="31"/>
-        <v>371</v>
+        <v>472</v>
       </c>
       <c r="I137">
         <f t="shared" si="32"/>
-        <v>156</v>
+        <v>293</v>
       </c>
       <c r="J137">
         <f t="shared" si="33"/>
-        <v>30</v>
+        <v>219</v>
       </c>
       <c r="M137">
         <f t="shared" si="28"/>
-        <v>2371</v>
+        <v>1414</v>
       </c>
       <c r="N137">
         <f t="shared" si="28"/>
-        <v>371</v>
+        <v>472</v>
       </c>
       <c r="O137">
         <f t="shared" si="28"/>
-        <v>156</v>
+        <v>293</v>
       </c>
       <c r="P137">
         <f t="shared" si="34"/>
-        <v>30</v>
+        <v>219</v>
       </c>
       <c r="Q137">
         <f t="shared" si="35"/>
-        <v>1431</v>
+        <v>652</v>
       </c>
       <c r="R137" t="b">
         <f t="shared" si="29"/>
@@ -8753,43 +8753,43 @@
         <v>0</v>
       </c>
       <c r="F138" s="2">
-        <v>100</v>
+        <v>194</v>
       </c>
       <c r="G138">
         <f t="shared" si="30"/>
-        <v>2343</v>
+        <v>1514</v>
       </c>
       <c r="H138">
         <f t="shared" si="31"/>
-        <v>360</v>
+        <v>277</v>
       </c>
       <c r="I138">
         <f t="shared" si="32"/>
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="J138">
         <f t="shared" si="33"/>
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="M138">
         <f t="shared" si="28"/>
-        <v>2343</v>
+        <v>1514</v>
       </c>
       <c r="N138">
         <f t="shared" si="28"/>
-        <v>360</v>
+        <v>277</v>
       </c>
       <c r="O138">
         <f t="shared" si="28"/>
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="P138">
         <f t="shared" si="34"/>
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="Q138">
         <f t="shared" si="35"/>
-        <v>1458</v>
+        <v>572</v>
       </c>
       <c r="R138" t="b">
         <f t="shared" si="29"/>
@@ -8814,43 +8814,43 @@
         <v>213</v>
       </c>
       <c r="F139" s="2">
-        <v>101</v>
+        <v>6</v>
       </c>
       <c r="G139">
         <f t="shared" si="30"/>
-        <v>2504</v>
+        <v>1748</v>
       </c>
       <c r="H139">
         <f t="shared" si="31"/>
-        <v>302</v>
+        <v>185</v>
       </c>
       <c r="I139">
         <f t="shared" si="32"/>
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="J139">
         <f t="shared" si="33"/>
-        <v>55</v>
+        <v>159</v>
       </c>
       <c r="M139">
         <f t="shared" si="28"/>
-        <v>2504</v>
+        <v>1748</v>
       </c>
       <c r="N139">
         <f t="shared" si="28"/>
-        <v>302</v>
+        <v>185</v>
       </c>
       <c r="O139">
         <f t="shared" si="28"/>
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="P139">
         <f t="shared" si="34"/>
-        <v>55</v>
+        <v>159</v>
       </c>
       <c r="Q139">
         <f t="shared" si="35"/>
-        <v>1293</v>
+        <v>401</v>
       </c>
       <c r="R139" t="b">
         <f t="shared" si="29"/>
@@ -8875,43 +8875,43 @@
         <v>164</v>
       </c>
       <c r="F140" s="2">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="G140">
         <f t="shared" si="30"/>
-        <v>2540</v>
+        <v>1795</v>
       </c>
       <c r="H140">
         <f t="shared" si="31"/>
-        <v>260</v>
+        <v>337</v>
       </c>
       <c r="I140">
         <f t="shared" si="32"/>
-        <v>326</v>
+        <v>169</v>
       </c>
       <c r="J140">
         <f t="shared" si="33"/>
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="M140">
         <f t="shared" si="28"/>
-        <v>2540</v>
+        <v>1795</v>
       </c>
       <c r="N140">
         <f t="shared" si="28"/>
-        <v>260</v>
+        <v>337</v>
       </c>
       <c r="O140">
         <f t="shared" si="28"/>
-        <v>326</v>
+        <v>169</v>
       </c>
       <c r="P140">
         <f t="shared" si="34"/>
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="Q140">
         <f t="shared" si="35"/>
-        <v>1256</v>
+        <v>286</v>
       </c>
       <c r="R140" t="b">
         <f t="shared" si="29"/>
@@ -8936,43 +8936,43 @@
         <v>283</v>
       </c>
       <c r="F141" s="2">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="G141">
         <f t="shared" si="30"/>
-        <v>2524</v>
+        <v>1913</v>
       </c>
       <c r="H141">
         <f t="shared" si="31"/>
-        <v>387</v>
+        <v>314</v>
       </c>
       <c r="I141">
         <f t="shared" si="32"/>
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J141">
         <f t="shared" si="33"/>
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="M141">
         <f t="shared" si="28"/>
-        <v>2524</v>
+        <v>1913</v>
       </c>
       <c r="N141">
         <f t="shared" si="28"/>
-        <v>387</v>
+        <v>314</v>
       </c>
       <c r="O141">
         <f t="shared" si="28"/>
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="P141">
         <f t="shared" si="34"/>
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="Q141">
         <f t="shared" si="35"/>
-        <v>1280</v>
+        <v>191</v>
       </c>
       <c r="R141" t="b">
         <f t="shared" si="29"/>
@@ -8997,43 +8997,43 @@
         <v>142</v>
       </c>
       <c r="F142" s="2">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="G142">
         <f t="shared" si="30"/>
-        <v>2685</v>
+        <v>2032</v>
       </c>
       <c r="H142">
         <f t="shared" si="31"/>
-        <v>520</v>
+        <v>230</v>
       </c>
       <c r="I142">
         <f t="shared" si="32"/>
-        <v>229</v>
+        <v>315</v>
       </c>
       <c r="J142">
         <f t="shared" si="33"/>
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="M142">
         <f t="shared" si="28"/>
-        <v>2685</v>
+        <v>2032</v>
       </c>
       <c r="N142">
         <f t="shared" si="28"/>
-        <v>520</v>
+        <v>230</v>
       </c>
       <c r="O142">
         <f t="shared" si="28"/>
-        <v>229</v>
+        <v>315</v>
       </c>
       <c r="P142">
         <f t="shared" si="34"/>
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="Q142">
         <f t="shared" si="35"/>
-        <v>1145</v>
+        <v>203</v>
       </c>
       <c r="R142" t="b">
         <f t="shared" si="29"/>
@@ -9058,43 +9058,43 @@
         <v>348</v>
       </c>
       <c r="F143" s="2">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="G143">
         <f t="shared" si="30"/>
-        <v>2769</v>
+        <v>2097</v>
       </c>
       <c r="H143">
         <f t="shared" si="31"/>
-        <v>430</v>
+        <v>299</v>
       </c>
       <c r="I143">
         <f t="shared" si="32"/>
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="J143">
         <f t="shared" si="33"/>
-        <v>300</v>
+        <v>135</v>
       </c>
       <c r="M143">
         <f t="shared" si="28"/>
-        <v>2769</v>
+        <v>2097</v>
       </c>
       <c r="N143">
         <f t="shared" si="28"/>
-        <v>430</v>
+        <v>299</v>
       </c>
       <c r="O143">
         <f t="shared" si="28"/>
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="P143">
         <f t="shared" si="34"/>
-        <v>300</v>
+        <v>1671</v>
       </c>
       <c r="Q143">
         <f t="shared" si="35"/>
-        <v>1044</v>
+        <v>135</v>
       </c>
       <c r="R143" t="b">
         <f t="shared" si="29"/>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="S143" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.3">
@@ -9118,48 +9118,45 @@
       <c r="D144">
         <v>286</v>
       </c>
-      <c r="F144" s="2">
-        <v>120</v>
-      </c>
-      <c r="G144">
+      <c r="G144" t="str">
         <f t="shared" si="30"/>
-        <v>3016</v>
-      </c>
-      <c r="H144">
+        <v/>
+      </c>
+      <c r="H144" t="str">
         <f t="shared" si="31"/>
-        <v>260</v>
-      </c>
-      <c r="I144">
+        <v/>
+      </c>
+      <c r="I144" t="str">
         <f t="shared" si="32"/>
-        <v>216</v>
-      </c>
-      <c r="J144">
+        <v/>
+      </c>
+      <c r="J144" t="str">
         <f t="shared" si="33"/>
-        <v>144</v>
+        <v/>
       </c>
       <c r="M144">
         <f t="shared" si="28"/>
-        <v>3016</v>
+        <v>1355</v>
       </c>
       <c r="N144">
         <f t="shared" si="28"/>
-        <v>260</v>
+        <v>1796</v>
       </c>
       <c r="O144">
         <f t="shared" si="28"/>
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="P144">
         <f t="shared" si="34"/>
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="Q144">
         <f t="shared" si="35"/>
-        <v>780</v>
+        <v>1539</v>
       </c>
       <c r="R144" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S144" t="b">
         <f t="shared" si="36"/>
@@ -9179,48 +9176,45 @@
       <c r="D145">
         <v>13</v>
       </c>
-      <c r="F145" s="2">
-        <v>44</v>
-      </c>
-      <c r="G145">
+      <c r="G145" t="str">
         <f t="shared" si="30"/>
-        <v>3134</v>
-      </c>
-      <c r="H145">
+        <v/>
+      </c>
+      <c r="H145" t="str">
         <f t="shared" si="31"/>
-        <v>177</v>
-      </c>
-      <c r="I145">
+        <v/>
+      </c>
+      <c r="I145" t="str">
         <f t="shared" si="32"/>
-        <v>321</v>
-      </c>
-      <c r="J145">
+        <v/>
+      </c>
+      <c r="J145" t="str">
         <f t="shared" si="33"/>
-        <v>244</v>
+        <v/>
       </c>
       <c r="M145">
         <f t="shared" si="28"/>
-        <v>3134</v>
+        <v>1355</v>
       </c>
       <c r="N145">
         <f t="shared" si="28"/>
-        <v>177</v>
+        <v>1796</v>
       </c>
       <c r="O145">
         <f t="shared" si="28"/>
-        <v>321</v>
+        <v>233</v>
       </c>
       <c r="P145">
         <f t="shared" si="34"/>
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="Q145">
         <f t="shared" si="35"/>
-        <v>665</v>
+        <v>1539</v>
       </c>
       <c r="R145" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S145" t="b">
         <f t="shared" si="36"/>
@@ -9240,48 +9234,45 @@
       <c r="D146">
         <v>76</v>
       </c>
-      <c r="F146" s="2">
-        <v>82</v>
-      </c>
-      <c r="G146">
+      <c r="G146" t="str">
         <f t="shared" si="30"/>
-        <v>3069</v>
-      </c>
-      <c r="H146">
+        <v/>
+      </c>
+      <c r="H146" t="str">
         <f t="shared" si="31"/>
-        <v>412</v>
-      </c>
-      <c r="I146">
+        <v/>
+      </c>
+      <c r="I146" t="str">
         <f t="shared" si="32"/>
-        <v>343</v>
-      </c>
-      <c r="J146">
+        <v/>
+      </c>
+      <c r="J146" t="str">
         <f t="shared" si="33"/>
-        <v>330</v>
+        <v/>
       </c>
       <c r="M146">
         <f t="shared" si="28"/>
-        <v>3069</v>
+        <v>1355</v>
       </c>
       <c r="N146">
         <f t="shared" si="28"/>
-        <v>412</v>
+        <v>1796</v>
       </c>
       <c r="O146">
         <f t="shared" si="28"/>
-        <v>343</v>
+        <v>233</v>
       </c>
       <c r="P146">
         <f t="shared" si="34"/>
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="Q146">
         <f t="shared" si="35"/>
-        <v>746</v>
+        <v>1539</v>
       </c>
       <c r="R146" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S146" t="b">
         <f t="shared" si="36"/>
@@ -9301,48 +9292,45 @@
       <c r="D147">
         <v>192</v>
       </c>
-      <c r="F147" s="2">
-        <v>78</v>
-      </c>
-      <c r="G147">
+      <c r="G147" t="str">
         <f t="shared" si="30"/>
-        <v>3399</v>
-      </c>
-      <c r="H147">
+        <v/>
+      </c>
+      <c r="H147" t="str">
         <f t="shared" si="31"/>
-        <v>405</v>
-      </c>
-      <c r="I147">
+        <v/>
+      </c>
+      <c r="I147" t="str">
         <f t="shared" si="32"/>
-        <v>146</v>
-      </c>
-      <c r="J147">
+        <v/>
+      </c>
+      <c r="J147" t="str">
         <f t="shared" si="33"/>
-        <v>135</v>
+        <v/>
       </c>
       <c r="M147">
         <f t="shared" si="28"/>
-        <v>3399</v>
+        <v>1355</v>
       </c>
       <c r="N147">
         <f t="shared" si="28"/>
-        <v>405</v>
+        <v>1796</v>
       </c>
       <c r="O147">
         <f t="shared" si="28"/>
-        <v>146</v>
+        <v>233</v>
       </c>
       <c r="P147">
         <f t="shared" si="34"/>
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="Q147">
         <f t="shared" si="35"/>
-        <v>428</v>
+        <v>1539</v>
       </c>
       <c r="R147" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S147" t="b">
         <f t="shared" si="36"/>
@@ -9362,48 +9350,45 @@
       <c r="D148">
         <v>140</v>
       </c>
-      <c r="F148" s="2">
-        <v>168</v>
-      </c>
-      <c r="G148">
+      <c r="G148" t="str">
         <f t="shared" si="30"/>
-        <v>3507</v>
-      </c>
-      <c r="H148">
+        <v/>
+      </c>
+      <c r="H148" t="str">
         <f t="shared" si="31"/>
-        <v>486</v>
-      </c>
-      <c r="I148">
+        <v/>
+      </c>
+      <c r="I148" t="str">
         <f t="shared" si="32"/>
-        <v>292</v>
-      </c>
-      <c r="J148">
+        <v/>
+      </c>
+      <c r="J148" t="str">
         <f t="shared" si="33"/>
-        <v>250</v>
+        <v/>
       </c>
       <c r="M148">
         <f t="shared" si="28"/>
-        <v>3507</v>
+        <v>1355</v>
       </c>
       <c r="N148">
         <f t="shared" si="28"/>
-        <v>486</v>
+        <v>1796</v>
       </c>
       <c r="O148">
         <f t="shared" si="28"/>
-        <v>292</v>
+        <v>233</v>
       </c>
       <c r="P148">
         <f t="shared" si="34"/>
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="Q148">
         <f t="shared" si="35"/>
-        <v>377</v>
+        <v>1539</v>
       </c>
       <c r="R148" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S148" t="b">
         <f t="shared" si="36"/>
@@ -9423,48 +9408,45 @@
       <c r="D149">
         <v>241</v>
       </c>
-      <c r="F149" s="2">
-        <v>31</v>
-      </c>
-      <c r="G149">
+      <c r="G149" t="str">
         <f t="shared" si="30"/>
-        <v>3697</v>
-      </c>
-      <c r="H149">
+        <v/>
+      </c>
+      <c r="H149" t="str">
         <f t="shared" si="31"/>
-        <v>324</v>
-      </c>
-      <c r="I149">
+        <v/>
+      </c>
+      <c r="I149" t="str">
         <f t="shared" si="32"/>
-        <v>327</v>
-      </c>
-      <c r="J149">
+        <v/>
+      </c>
+      <c r="J149" t="str">
         <f t="shared" si="33"/>
-        <v>84</v>
+        <v/>
       </c>
       <c r="M149">
         <f t="shared" si="28"/>
-        <v>3697</v>
+        <v>1355</v>
       </c>
       <c r="N149">
         <f t="shared" si="28"/>
-        <v>324</v>
+        <v>1796</v>
       </c>
       <c r="O149">
         <f t="shared" si="28"/>
-        <v>327</v>
+        <v>233</v>
       </c>
       <c r="P149">
         <f t="shared" si="34"/>
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="Q149">
         <f t="shared" si="35"/>
-        <v>127</v>
+        <v>1539</v>
       </c>
       <c r="R149" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S149" t="b">
         <f t="shared" si="36"/>
@@ -9484,48 +9466,45 @@
       <c r="D150">
         <v>208</v>
       </c>
-      <c r="F150" s="2">
-        <v>13</v>
-      </c>
-      <c r="G150">
+      <c r="G150" t="str">
         <f t="shared" si="30"/>
-        <v>3741</v>
-      </c>
-      <c r="H150">
+        <v/>
+      </c>
+      <c r="H150" t="str">
         <f t="shared" si="31"/>
-        <v>252</v>
-      </c>
-      <c r="I150">
+        <v/>
+      </c>
+      <c r="I150" t="str">
         <f t="shared" si="32"/>
-        <v>94</v>
-      </c>
-      <c r="J150">
+        <v/>
+      </c>
+      <c r="J150" t="str">
         <f t="shared" si="33"/>
-        <v>307</v>
+        <v/>
       </c>
       <c r="M150">
         <f t="shared" si="28"/>
-        <v>3741</v>
+        <v>1355</v>
       </c>
       <c r="N150">
         <f t="shared" si="28"/>
-        <v>252</v>
+        <v>1796</v>
       </c>
       <c r="O150">
         <f t="shared" si="28"/>
-        <v>94</v>
+        <v>233</v>
       </c>
       <c r="P150">
         <f t="shared" si="34"/>
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="Q150">
         <f t="shared" si="35"/>
-        <v>56</v>
+        <v>1539</v>
       </c>
       <c r="R150" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S150" t="b">
         <f t="shared" si="36"/>
@@ -9545,48 +9524,45 @@
       <c r="D151">
         <v>107</v>
       </c>
-      <c r="F151" s="2">
-        <v>16</v>
-      </c>
-      <c r="G151">
+      <c r="G151" t="str">
         <f t="shared" si="30"/>
-        <v>3562</v>
-      </c>
-      <c r="H151">
+        <v/>
+      </c>
+      <c r="H151" t="str">
         <f t="shared" si="31"/>
-        <v>3</v>
-      </c>
-      <c r="I151">
+        <v/>
+      </c>
+      <c r="I151" t="str">
         <f t="shared" si="32"/>
-        <v>213</v>
-      </c>
-      <c r="J151">
+        <v/>
+      </c>
+      <c r="J151" t="str">
         <f t="shared" si="33"/>
-        <v>64</v>
+        <v/>
       </c>
       <c r="M151">
         <f t="shared" si="28"/>
-        <v>3562</v>
+        <v>1355</v>
       </c>
       <c r="N151">
         <f t="shared" si="28"/>
-        <v>3</v>
+        <v>1796</v>
       </c>
       <c r="O151">
         <f t="shared" si="28"/>
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="P151">
         <f t="shared" si="34"/>
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="Q151">
         <f t="shared" si="35"/>
-        <v>336</v>
+        <v>1539</v>
       </c>
       <c r="R151" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S151" t="b">
         <f t="shared" si="36"/>
@@ -9606,48 +9582,45 @@
       <c r="D152">
         <v>134</v>
       </c>
-      <c r="F152" s="2">
-        <v>88</v>
-      </c>
-      <c r="G152">
+      <c r="G152" t="str">
         <f t="shared" si="30"/>
-        <v>3626</v>
-      </c>
-      <c r="H152">
+        <v/>
+      </c>
+      <c r="H152" t="str">
         <f t="shared" si="31"/>
-        <v>4</v>
-      </c>
-      <c r="I152">
+        <v/>
+      </c>
+      <c r="I152" t="str">
         <f t="shared" si="32"/>
-        <v>210</v>
-      </c>
-      <c r="J152">
+        <v/>
+      </c>
+      <c r="J152" t="str">
         <f t="shared" si="33"/>
-        <v>113</v>
+        <v/>
       </c>
       <c r="M152">
         <f t="shared" si="28"/>
-        <v>3626</v>
+        <v>1355</v>
       </c>
       <c r="N152">
         <f t="shared" si="28"/>
-        <v>4</v>
+        <v>1796</v>
       </c>
       <c r="O152">
         <f t="shared" si="28"/>
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="P152">
         <f t="shared" si="34"/>
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="Q152">
         <f t="shared" si="35"/>
-        <v>294</v>
+        <v>1539</v>
       </c>
       <c r="R152" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S152" t="b">
         <f t="shared" si="36"/>
@@ -9667,48 +9640,45 @@
       <c r="D153">
         <v>326</v>
       </c>
-      <c r="F153" s="2">
-        <v>171</v>
-      </c>
-      <c r="G153">
+      <c r="G153" t="str">
         <f t="shared" si="30"/>
-        <v>3726</v>
-      </c>
-      <c r="H153">
+        <v/>
+      </c>
+      <c r="H153" t="str">
         <f t="shared" si="31"/>
-        <v>56</v>
-      </c>
-      <c r="I153">
+        <v/>
+      </c>
+      <c r="I153" t="str">
         <f t="shared" si="32"/>
-        <v>125</v>
-      </c>
-      <c r="J153">
+        <v/>
+      </c>
+      <c r="J153" t="str">
         <f t="shared" si="33"/>
-        <v>164</v>
+        <v/>
       </c>
       <c r="M153">
         <f t="shared" si="28"/>
-        <v>3726</v>
+        <v>1355</v>
       </c>
       <c r="N153">
         <f t="shared" si="28"/>
-        <v>56</v>
+        <v>1796</v>
       </c>
       <c r="O153">
         <f t="shared" si="28"/>
-        <v>125</v>
+        <v>233</v>
       </c>
       <c r="P153">
         <f t="shared" si="34"/>
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="Q153">
         <f t="shared" si="35"/>
-        <v>201</v>
+        <v>1539</v>
       </c>
       <c r="R153" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S153" t="b">
         <f t="shared" si="36"/>
@@ -9728,52 +9698,49 @@
       <c r="D154">
         <v>94</v>
       </c>
-      <c r="F154" s="2">
-        <v>113</v>
-      </c>
-      <c r="G154">
+      <c r="G154" t="str">
         <f t="shared" si="30"/>
-        <v>3819</v>
-      </c>
-      <c r="H154">
+        <v/>
+      </c>
+      <c r="H154" t="str">
         <f t="shared" si="31"/>
-        <v>191</v>
-      </c>
-      <c r="I154">
+        <v/>
+      </c>
+      <c r="I154" t="str">
         <f t="shared" si="32"/>
-        <v>34</v>
-      </c>
-      <c r="J154">
+        <v/>
+      </c>
+      <c r="J154" t="str">
         <f t="shared" si="33"/>
-        <v>58</v>
+        <v/>
       </c>
       <c r="M154">
         <f t="shared" si="28"/>
-        <v>3819</v>
+        <v>1355</v>
       </c>
       <c r="N154">
         <f t="shared" si="28"/>
-        <v>191</v>
+        <v>1796</v>
       </c>
       <c r="O154">
         <f t="shared" si="28"/>
-        <v>34</v>
+        <v>233</v>
       </c>
       <c r="P154">
         <f t="shared" si="34"/>
-        <v>2941</v>
+        <v>0</v>
       </c>
       <c r="Q154">
         <f t="shared" si="35"/>
-        <v>58</v>
+        <v>1539</v>
       </c>
       <c r="R154" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S154" t="b">
         <f t="shared" si="36"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.3">
@@ -9823,7 +9790,7 @@
       </c>
       <c r="Q155">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R155" t="b">
         <f t="shared" si="29"/>
@@ -9881,7 +9848,7 @@
       </c>
       <c r="Q156">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R156" t="b">
         <f t="shared" si="29"/>
@@ -9939,7 +9906,7 @@
       </c>
       <c r="Q157">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R157" t="b">
         <f t="shared" si="29"/>
@@ -9997,7 +9964,7 @@
       </c>
       <c r="Q158">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R158" t="b">
         <f t="shared" si="29"/>
@@ -10055,7 +10022,7 @@
       </c>
       <c r="Q159">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R159" t="b">
         <f t="shared" si="29"/>
@@ -10113,7 +10080,7 @@
       </c>
       <c r="Q160">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R160" t="b">
         <f t="shared" si="29"/>
@@ -10171,7 +10138,7 @@
       </c>
       <c r="Q161">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R161" t="b">
         <f t="shared" si="29"/>
@@ -10229,7 +10196,7 @@
       </c>
       <c r="Q162">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R162" t="b">
         <f t="shared" si="29"/>
@@ -10287,7 +10254,7 @@
       </c>
       <c r="Q163">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R163" t="b">
         <f t="shared" ref="R163:R194" si="37">F163=""</f>
@@ -10345,7 +10312,7 @@
       </c>
       <c r="Q164">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R164" t="b">
         <f t="shared" si="37"/>
@@ -10403,7 +10370,7 @@
       </c>
       <c r="Q165">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R165" t="b">
         <f t="shared" si="37"/>
@@ -10461,7 +10428,7 @@
       </c>
       <c r="Q166">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R166" t="b">
         <f t="shared" si="37"/>
@@ -10519,7 +10486,7 @@
       </c>
       <c r="Q167">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R167" t="b">
         <f t="shared" si="37"/>
@@ -10577,7 +10544,7 @@
       </c>
       <c r="Q168">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R168" t="b">
         <f t="shared" si="37"/>
@@ -10635,7 +10602,7 @@
       </c>
       <c r="Q169">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R169" t="b">
         <f t="shared" si="37"/>
@@ -10693,7 +10660,7 @@
       </c>
       <c r="Q170">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R170" t="b">
         <f t="shared" si="37"/>
@@ -10751,7 +10718,7 @@
       </c>
       <c r="Q171">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R171" t="b">
         <f t="shared" si="37"/>
@@ -10809,7 +10776,7 @@
       </c>
       <c r="Q172">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R172" t="b">
         <f t="shared" si="37"/>
@@ -10867,7 +10834,7 @@
       </c>
       <c r="Q173">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R173" t="b">
         <f t="shared" si="37"/>
@@ -10925,7 +10892,7 @@
       </c>
       <c r="Q174">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R174" t="b">
         <f t="shared" si="37"/>
@@ -10983,7 +10950,7 @@
       </c>
       <c r="Q175">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R175" t="b">
         <f t="shared" si="37"/>
@@ -11041,7 +11008,7 @@
       </c>
       <c r="Q176">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R176" t="b">
         <f t="shared" si="37"/>
@@ -11099,7 +11066,7 @@
       </c>
       <c r="Q177">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R177" t="b">
         <f t="shared" si="37"/>
@@ -11157,7 +11124,7 @@
       </c>
       <c r="Q178">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R178" t="b">
         <f t="shared" si="37"/>
@@ -11215,7 +11182,7 @@
       </c>
       <c r="Q179">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R179" t="b">
         <f t="shared" si="37"/>
@@ -11273,7 +11240,7 @@
       </c>
       <c r="Q180">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R180" t="b">
         <f t="shared" si="37"/>
@@ -11331,7 +11298,7 @@
       </c>
       <c r="Q181">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R181" t="b">
         <f t="shared" si="37"/>
@@ -11389,7 +11356,7 @@
       </c>
       <c r="Q182">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R182" t="b">
         <f t="shared" si="37"/>
@@ -11447,7 +11414,7 @@
       </c>
       <c r="Q183">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R183" t="b">
         <f t="shared" si="37"/>
@@ -11505,7 +11472,7 @@
       </c>
       <c r="Q184">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R184" t="b">
         <f t="shared" si="37"/>
@@ -11563,7 +11530,7 @@
       </c>
       <c r="Q185">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R185" t="b">
         <f t="shared" si="37"/>
@@ -11621,7 +11588,7 @@
       </c>
       <c r="Q186">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R186" t="b">
         <f t="shared" si="37"/>
@@ -11679,7 +11646,7 @@
       </c>
       <c r="Q187">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R187" t="b">
         <f t="shared" si="37"/>
@@ -11737,7 +11704,7 @@
       </c>
       <c r="Q188">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R188" t="b">
         <f t="shared" si="37"/>
@@ -11795,7 +11762,7 @@
       </c>
       <c r="Q189">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R189" t="b">
         <f t="shared" si="37"/>
@@ -11853,7 +11820,7 @@
       </c>
       <c r="Q190">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R190" t="b">
         <f t="shared" si="37"/>
@@ -11911,7 +11878,7 @@
       </c>
       <c r="Q191">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R191" t="b">
         <f t="shared" si="37"/>
@@ -11969,7 +11936,7 @@
       </c>
       <c r="Q192">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R192" t="b">
         <f t="shared" si="37"/>
@@ -12027,7 +11994,7 @@
       </c>
       <c r="Q193">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R193" t="b">
         <f t="shared" si="37"/>
@@ -12085,7 +12052,7 @@
       </c>
       <c r="Q194">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R194" t="b">
         <f t="shared" si="37"/>
@@ -12143,7 +12110,7 @@
       </c>
       <c r="Q195">
         <f t="shared" si="35"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R195" t="b">
         <f t="shared" ref="R195:R202" si="39">F195=""</f>
@@ -12201,7 +12168,7 @@
       </c>
       <c r="Q196">
         <f t="shared" ref="Q196:Q202" si="45">INT(SQRT((M$3-M196)*(M$3-M196)+(N$3-N196)*(N$3-N196)) +0.5)</f>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R196" t="b">
         <f t="shared" si="39"/>
@@ -12259,7 +12226,7 @@
       </c>
       <c r="Q197">
         <f t="shared" si="45"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R197" t="b">
         <f t="shared" si="39"/>
@@ -12317,7 +12284,7 @@
       </c>
       <c r="Q198">
         <f t="shared" si="45"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R198" t="b">
         <f t="shared" si="39"/>
@@ -12375,7 +12342,7 @@
       </c>
       <c r="Q199">
         <f t="shared" si="45"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R199" t="b">
         <f t="shared" si="39"/>
@@ -12433,7 +12400,7 @@
       </c>
       <c r="Q200">
         <f t="shared" si="45"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R200" t="b">
         <f t="shared" si="39"/>
@@ -12491,7 +12458,7 @@
       </c>
       <c r="Q201">
         <f t="shared" si="45"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R201" t="b">
         <f t="shared" si="39"/>
@@ -12549,7 +12516,7 @@
       </c>
       <c r="Q202">
         <f t="shared" si="45"/>
-        <v>2893</v>
+        <v>1539</v>
       </c>
       <c r="R202" t="b">
         <f t="shared" si="39"/>
